--- a/Scenario Files/TestScenarios.xlsx
+++ b/Scenario Files/TestScenarios.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Square Footage</t>
+          <t>square_footage</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Household Size</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -459,12 +459,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Outdoor Temp</t>
+          <t>outdoor_temp</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>House Age</t>
+          <t>hvac_age</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -536,8 +536,6 @@
       <c r="J2" t="n">
         <v>22</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>78</t>
@@ -597,8 +595,6 @@
       <c r="J3" t="n">
         <v>27</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>72</t>
@@ -658,8 +654,6 @@
       <c r="J4" t="n">
         <v>37</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>77</t>
@@ -719,8 +713,6 @@
       <c r="J5" t="n">
         <v>42</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>74</t>
@@ -780,8 +772,6 @@
       <c r="J6" t="n">
         <v>47</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>64</t>
@@ -841,8 +831,6 @@
       <c r="J7" t="n">
         <v>23</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>76</t>
@@ -902,8 +890,6 @@
       <c r="J8" t="n">
         <v>23</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>67</t>
@@ -963,8 +949,6 @@
       <c r="J9" t="n">
         <v>17</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>68</t>
@@ -1024,8 +1008,6 @@
       <c r="J10" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>76</t>
@@ -1085,8 +1067,6 @@
       <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>66</t>
@@ -1146,8 +1126,6 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>73</t>
@@ -1207,8 +1185,6 @@
       <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>75</t>
@@ -1268,8 +1244,6 @@
       <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>78</t>
@@ -1329,8 +1303,6 @@
       <c r="J15" t="n">
         <v>12</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>66</t>
@@ -1390,8 +1362,6 @@
       <c r="J16" t="n">
         <v>15</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>65</t>
@@ -1451,8 +1421,6 @@
       <c r="J17" t="n">
         <v>19</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>75</t>
@@ -1512,8 +1480,6 @@
       <c r="J18" t="n">
         <v>19</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>66</t>
@@ -1573,8 +1539,6 @@
       <c r="J19" t="n">
         <v>21</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>78</t>
@@ -1634,8 +1598,6 @@
       <c r="J20" t="n">
         <v>25</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>76</t>
@@ -1695,8 +1657,6 @@
       <c r="J21" t="n">
         <v>29</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>66</t>
@@ -1756,8 +1716,6 @@
       <c r="J22" t="n">
         <v>102</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>66</t>
@@ -1817,8 +1775,6 @@
       <c r="J23" t="n">
         <v>40</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>78</t>
@@ -1878,8 +1834,6 @@
       <c r="J24" t="n">
         <v>35</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>79</t>
@@ -1939,8 +1893,6 @@
       <c r="J25" t="n">
         <v>20</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>77</t>
@@ -2000,8 +1952,6 @@
       <c r="J26" t="n">
         <v>10</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>82</t>
@@ -2061,8 +2011,6 @@
       <c r="J27" t="n">
         <v>28</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>78</t>
@@ -2122,8 +2070,6 @@
       <c r="J28" t="n">
         <v>30</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>79</t>
@@ -2183,8 +2129,6 @@
       <c r="J29" t="n">
         <v>32</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>78</t>
@@ -2244,8 +2188,6 @@
       <c r="J30" t="n">
         <v>28</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>60</t>
@@ -2305,8 +2247,6 @@
       <c r="J31" t="n">
         <v>15</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>73</t>
@@ -2366,8 +2306,6 @@
       <c r="J32" t="n">
         <v>10</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>74</t>
@@ -2427,8 +2365,6 @@
       <c r="J33" t="n">
         <v>20</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>66</t>
@@ -2488,8 +2424,6 @@
       <c r="J34" t="n">
         <v>30</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>65</t>
@@ -2549,8 +2483,6 @@
       <c r="J35" t="n">
         <v>22</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>66</t>
@@ -2610,8 +2542,6 @@
       <c r="J36" t="n">
         <v>20</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>71</t>
@@ -2671,8 +2601,6 @@
       <c r="J37" t="n">
         <v>40</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>65</t>
@@ -2732,8 +2660,6 @@
       <c r="J38" t="n">
         <v>22</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>78</t>
@@ -2793,8 +2719,6 @@
       <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>78</t>
@@ -2854,8 +2778,6 @@
       <c r="J40" t="n">
         <v>8</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>73</t>
@@ -2915,8 +2837,6 @@
       <c r="J41" t="n">
         <v>20</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>65</t>
@@ -2976,8 +2896,6 @@
       <c r="J42" t="n">
         <v>24</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>66</t>
@@ -3037,8 +2955,6 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>67</t>
@@ -3098,8 +3014,6 @@
       <c r="J44" t="n">
         <v>3</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>66</t>
@@ -3159,8 +3073,6 @@
       <c r="J45" t="n">
         <v>24</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>70</t>
@@ -3220,8 +3132,6 @@
       <c r="J46" t="n">
         <v>48</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>74</t>
@@ -3281,8 +3191,6 @@
       <c r="J47" t="n">
         <v>15</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>68</t>
@@ -3342,8 +3250,6 @@
       <c r="J48" t="n">
         <v>18</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>66</t>
@@ -3403,8 +3309,6 @@
       <c r="J49" t="n">
         <v>29</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>65</t>
@@ -3464,8 +3368,6 @@
       <c r="J50" t="n">
         <v>14</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>66</t>
@@ -3525,8 +3427,6 @@
       <c r="J51" t="n">
         <v>74</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>68</t>
@@ -3586,8 +3486,6 @@
       <c r="J52" t="n">
         <v>16</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>72</t>
@@ -3647,8 +3545,6 @@
       <c r="J53" t="n">
         <v>7</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>72</t>
@@ -3708,8 +3604,6 @@
       <c r="J54" t="n">
         <v>86</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>73</t>
@@ -3769,8 +3663,6 @@
       <c r="J55" t="n">
         <v>41</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>62</t>
@@ -3830,8 +3722,6 @@
       <c r="J56" t="n">
         <v>12</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>66</t>
@@ -3864,8 +3754,6 @@
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
         <v>2</v>
       </c>
@@ -3879,8 +3767,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
         <v>4</v>
       </c>
@@ -3921,8 +3807,6 @@
           <t>Monroeville, PA</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
         <v>3</v>
       </c>
@@ -3936,8 +3820,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
         <v>8</v>
       </c>
@@ -3978,8 +3860,6 @@
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
         <v>2</v>
       </c>
@@ -3993,8 +3873,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>15</v>
       </c>
@@ -4035,8 +3913,6 @@
           <t>Monroeville, PA</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
         <v>5</v>
       </c>
@@ -4050,8 +3926,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
         <v>10</v>
       </c>
@@ -4092,8 +3966,6 @@
           <t>Indiana, PA</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
         <v>4</v>
       </c>
@@ -4107,8 +3979,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
         <v>7</v>
       </c>
@@ -4149,8 +4019,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
         <v>4</v>
       </c>
@@ -4164,8 +4032,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
         <v>7</v>
       </c>
@@ -4206,8 +4072,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
         <v>3</v>
       </c>
@@ -4221,8 +4085,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
         <v>10</v>
       </c>
@@ -4263,8 +4125,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
         <v>3</v>
       </c>
@@ -4278,8 +4138,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
         <v>2</v>
       </c>
@@ -4320,8 +4178,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
         <v>4</v>
       </c>
@@ -4335,8 +4191,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
         <v>6</v>
       </c>
@@ -4377,8 +4231,6 @@
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
         <v>3</v>
       </c>
@@ -4392,8 +4244,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
         <v>4</v>
       </c>
@@ -4434,8 +4284,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
         <v>3</v>
       </c>
@@ -4449,8 +4297,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
         <v>12</v>
       </c>
@@ -4491,8 +4337,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
         <v>5</v>
       </c>
@@ -4506,8 +4350,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
         <v>6</v>
       </c>
@@ -4548,8 +4390,6 @@
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
         <v>3</v>
       </c>
@@ -4563,8 +4403,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
         <v>12</v>
       </c>
@@ -4605,8 +4443,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
         <v>4</v>
       </c>
@@ -4620,8 +4456,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="n">
         <v>7</v>
       </c>
@@ -4662,8 +4496,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
         <v>2</v>
       </c>
@@ -4677,8 +4509,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="n">
         <v>15</v>
       </c>
@@ -4719,8 +4549,6 @@
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
         <v>5</v>
       </c>
@@ -4734,8 +4562,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
         <v>4</v>
       </c>
@@ -4776,8 +4602,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
         <v>3</v>
       </c>
@@ -4791,8 +4615,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
         <v>3</v>
       </c>
@@ -4833,8 +4655,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
         <v>4</v>
       </c>
@@ -4848,8 +4668,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
         <v>15</v>
       </c>
@@ -4890,8 +4708,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
         <v>4</v>
       </c>
@@ -4905,8 +4721,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
         <v>6</v>
       </c>
@@ -4947,8 +4761,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
         <v>4</v>
       </c>
@@ -4962,8 +4774,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
         <v>12</v>
       </c>
@@ -5004,8 +4814,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>3</v>
       </c>
@@ -5019,8 +4827,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
         <v>8</v>
       </c>
@@ -5061,8 +4867,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>4</v>
       </c>
@@ -5076,8 +4880,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
         <v>3</v>
       </c>
@@ -5118,8 +4920,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>2</v>
       </c>
@@ -5133,8 +4933,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
         <v>5</v>
       </c>
@@ -5175,8 +4973,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
       </c>
@@ -5190,8 +4986,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
         <v>6</v>
       </c>
@@ -5232,8 +5026,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>2</v>
       </c>
@@ -5247,8 +5039,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
         <v>10</v>
       </c>
@@ -5289,8 +5079,6 @@
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>2</v>
       </c>
@@ -5304,8 +5092,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
         <v>2</v>
       </c>
@@ -5346,8 +5132,6 @@
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>4</v>
       </c>
@@ -5361,8 +5145,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
         <v>8</v>
       </c>
@@ -5403,8 +5185,6 @@
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
       </c>
@@ -5418,8 +5198,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
         <v>10</v>
       </c>
@@ -5460,8 +5238,6 @@
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>5</v>
       </c>
@@ -5475,8 +5251,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="n">
         <v>6</v>
       </c>
@@ -5517,8 +5291,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>2</v>
       </c>
@@ -5532,8 +5304,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
         <v>10</v>
       </c>
@@ -5574,8 +5344,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
         <v>3</v>
       </c>
@@ -5589,8 +5357,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
         <v>5</v>
       </c>
@@ -5631,8 +5397,6 @@
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
         <v>3</v>
       </c>
@@ -5646,8 +5410,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
         <v>4</v>
       </c>
@@ -5688,8 +5450,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
         <v>2</v>
       </c>
@@ -5703,8 +5463,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
         <v>5</v>
       </c>
@@ -5745,8 +5503,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
         <v>4</v>
       </c>
@@ -5760,8 +5516,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="n">
         <v>4</v>
       </c>
@@ -5802,8 +5556,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
         <v>3</v>
       </c>
@@ -5817,8 +5569,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
         <v>6</v>
       </c>
@@ -5859,8 +5609,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
         <v>3</v>
       </c>
@@ -5874,8 +5622,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
         <v>8</v>
       </c>
@@ -5916,8 +5662,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
         <v>2</v>
       </c>
@@ -5931,8 +5675,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="n">
         <v>3</v>
       </c>
@@ -5973,8 +5715,6 @@
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
         <v>3</v>
       </c>
@@ -5988,8 +5728,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
         <v>1</v>
       </c>
@@ -6030,8 +5768,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
         <v>4</v>
       </c>
@@ -6045,8 +5781,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
         <v>15</v>
       </c>
@@ -6087,8 +5821,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
         <v>3</v>
       </c>
@@ -6102,8 +5834,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
         <v>5</v>
       </c>
@@ -6144,8 +5874,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
         <v>4</v>
       </c>
@@ -6159,8 +5887,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
         <v>6</v>
       </c>
@@ -6201,8 +5927,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
         <v>2</v>
       </c>
@@ -6216,8 +5940,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
         <v>4</v>
       </c>
@@ -6258,8 +5980,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="n">
         <v>2</v>
       </c>
@@ -6273,8 +5993,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
         <v>8</v>
       </c>
@@ -6315,8 +6033,6 @@
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
         <v>3</v>
       </c>
@@ -6330,8 +6046,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
         <v>5</v>
       </c>
@@ -6372,8 +6086,6 @@
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
         <v>5</v>
       </c>
@@ -6387,8 +6099,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
         <v>4</v>
       </c>
@@ -6429,8 +6139,6 @@
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
         <v>5</v>
       </c>
@@ -6444,8 +6152,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
         <v>5</v>
       </c>
@@ -6486,8 +6192,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
         <v>5</v>
       </c>
@@ -6501,8 +6205,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
         <v>3</v>
       </c>
@@ -6543,8 +6245,6 @@
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
         <v>4</v>
       </c>
@@ -6558,8 +6258,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
         <v>6</v>
       </c>
@@ -6600,8 +6298,6 @@
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
         <v>4</v>
       </c>
@@ -6615,8 +6311,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
         <v>8</v>
       </c>
@@ -6657,8 +6351,6 @@
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
         <v>3</v>
       </c>
@@ -6672,8 +6364,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
         <v>6</v>
       </c>
@@ -6714,8 +6404,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
         <v>2</v>
       </c>
@@ -6732,7 +6420,6 @@
       <c r="I107" t="n">
         <v>28</v>
       </c>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
         <v>105</v>
       </c>
@@ -6773,8 +6460,6 @@
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
         <v>2</v>
       </c>
@@ -6791,7 +6476,6 @@
       <c r="I108" t="n">
         <v>75</v>
       </c>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
         <v>120</v>
       </c>
@@ -6832,8 +6516,6 @@
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
         <v>4</v>
       </c>
@@ -6850,7 +6532,6 @@
       <c r="I109" t="n">
         <v>78</v>
       </c>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
         <v>130</v>
       </c>
@@ -6891,8 +6572,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
         <v>4</v>
       </c>
@@ -6909,7 +6588,6 @@
       <c r="I110" t="n">
         <v>28</v>
       </c>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
         <v>120</v>
       </c>
@@ -6950,8 +6628,6 @@
           <t>Uniontown, PA</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
         <v>2</v>
       </c>
@@ -6968,7 +6644,6 @@
       <c r="I111" t="n">
         <v>32</v>
       </c>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
         <v>120</v>
       </c>
@@ -7009,8 +6684,6 @@
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
         <v>5</v>
       </c>
@@ -7027,7 +6700,6 @@
       <c r="I112" t="n">
         <v>30</v>
       </c>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
         <v>120</v>
       </c>
@@ -7068,8 +6740,6 @@
           <t>Reading, PA</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
         <v>5</v>
       </c>
@@ -7086,7 +6756,6 @@
       <c r="I113" t="n">
         <v>82</v>
       </c>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
         <v>120</v>
       </c>
@@ -7127,8 +6796,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
         <v>5</v>
       </c>
@@ -7145,7 +6812,6 @@
       <c r="I114" t="n">
         <v>20</v>
       </c>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="n">
         <v>135</v>
       </c>
@@ -7186,8 +6852,6 @@
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
         <v>4</v>
       </c>
@@ -7204,7 +6868,6 @@
       <c r="I115" t="n">
         <v>30</v>
       </c>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="n">
         <v>120</v>
       </c>
@@ -7245,8 +6908,6 @@
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
         <v>3</v>
       </c>
@@ -7263,7 +6924,6 @@
       <c r="I116" t="n">
         <v>85</v>
       </c>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
         <v>120</v>
       </c>
@@ -7304,8 +6964,6 @@
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
         <v>6</v>
       </c>
@@ -7322,7 +6980,6 @@
       <c r="I117" t="n">
         <v>15</v>
       </c>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
         <v>135</v>
       </c>
@@ -7363,8 +7020,6 @@
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
         <v>2</v>
       </c>
@@ -7381,7 +7036,6 @@
       <c r="I118" t="n">
         <v>78</v>
       </c>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="n">
         <v>120</v>
       </c>
@@ -7422,8 +7076,6 @@
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
         <v>5</v>
       </c>
@@ -7440,7 +7092,6 @@
       <c r="I119" t="n">
         <v>88</v>
       </c>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
         <v>140</v>
       </c>
@@ -7481,8 +7132,6 @@
           <t>Newtown, PA</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
         <v>4</v>
       </c>
@@ -7499,7 +7148,6 @@
       <c r="I120" t="n">
         <v>22</v>
       </c>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
         <v>105</v>
       </c>
@@ -7540,8 +7188,6 @@
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
         <v>3</v>
       </c>
@@ -7558,7 +7204,6 @@
       <c r="I121" t="n">
         <v>30</v>
       </c>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
         <v>120</v>
       </c>
@@ -7599,8 +7244,6 @@
           <t>Chambersburg, PA</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
         <v>4</v>
       </c>
@@ -7617,7 +7260,6 @@
       <c r="I122" t="n">
         <v>55</v>
       </c>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="n">
         <v>120</v>
       </c>
@@ -7658,8 +7300,6 @@
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>4</v>
       </c>
@@ -7676,7 +7316,6 @@
       <c r="I123" t="n">
         <v>58</v>
       </c>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="n">
         <v>120</v>
       </c>
@@ -7717,8 +7356,6 @@
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>2</v>
       </c>
@@ -7735,7 +7372,6 @@
       <c r="I124" t="n">
         <v>65</v>
       </c>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
         <v>120</v>
       </c>
@@ -7776,8 +7412,6 @@
           <t>Monroeville, PA</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>4</v>
       </c>
@@ -7794,7 +7428,6 @@
       <c r="I125" t="n">
         <v>50</v>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="n">
         <v>120</v>
       </c>
@@ -7835,8 +7468,6 @@
           <t>Carlisle, PA</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>3</v>
       </c>
@@ -7853,7 +7484,6 @@
       <c r="I126" t="n">
         <v>72</v>
       </c>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="n">
         <v>120</v>
       </c>
@@ -7894,8 +7524,6 @@
           <t>Coatesville, PA</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>2</v>
       </c>
@@ -7912,7 +7540,6 @@
       <c r="I127" t="n">
         <v>52</v>
       </c>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
         <v>105</v>
       </c>
@@ -7953,8 +7580,6 @@
           <t>DuBois, PA</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
         <v>3</v>
       </c>
@@ -7971,7 +7596,6 @@
       <c r="I128" t="n">
         <v>45</v>
       </c>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
         <v>105</v>
       </c>
@@ -8012,8 +7636,6 @@
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
         <v>3</v>
       </c>
@@ -8030,7 +7652,6 @@
       <c r="I129" t="n">
         <v>55</v>
       </c>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="n">
         <v>130</v>
       </c>
@@ -8071,8 +7692,6 @@
           <t>Butler, PA</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
         <v>5</v>
       </c>
@@ -8089,7 +7708,6 @@
       <c r="I130" t="n">
         <v>55</v>
       </c>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="n">
         <v>120</v>
       </c>
@@ -8130,8 +7748,6 @@
           <t>Indiana, PA</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
         <v>6</v>
       </c>
@@ -8148,7 +7764,6 @@
       <c r="I131" t="n">
         <v>60</v>
       </c>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
         <v>120</v>
       </c>
@@ -8189,8 +7804,6 @@
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
         <v>3</v>
       </c>
@@ -8207,7 +7820,6 @@
       <c r="I132" t="n">
         <v>92</v>
       </c>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
         <v>120</v>
       </c>
@@ -8248,8 +7860,6 @@
           <t>Carlisle, PA</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
         <v>2</v>
       </c>
@@ -8266,7 +7876,6 @@
       <c r="I133" t="n">
         <v>42</v>
       </c>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="n">
         <v>120</v>
       </c>
@@ -8307,8 +7916,6 @@
           <t>DuBois, PA</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
         <v>5</v>
       </c>
@@ -8325,7 +7932,6 @@
       <c r="I134" t="n">
         <v>38</v>
       </c>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="n">
         <v>120</v>
       </c>
@@ -8366,8 +7972,6 @@
           <t>Gettysburg, PA</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
         <v>3</v>
       </c>
@@ -8384,7 +7988,6 @@
       <c r="I135" t="n">
         <v>55</v>
       </c>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="n">
         <v>120</v>
       </c>
@@ -8425,8 +8028,6 @@
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>2</v>
       </c>
@@ -8443,7 +8044,6 @@
       <c r="I136" t="n">
         <v>62</v>
       </c>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
         <v>120</v>
       </c>
@@ -8484,8 +8084,6 @@
           <t>Butler, PA</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
         <v>3</v>
       </c>
@@ -8502,7 +8100,6 @@
       <c r="I137" t="n">
         <v>50</v>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="n">
         <v>105</v>
       </c>
@@ -8543,8 +8140,6 @@
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>2</v>
       </c>
@@ -8561,7 +8156,6 @@
       <c r="I138" t="n">
         <v>58</v>
       </c>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
         <v>135</v>
       </c>
@@ -8602,8 +8196,6 @@
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>4</v>
       </c>
@@ -8620,7 +8212,6 @@
       <c r="I139" t="n">
         <v>55</v>
       </c>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="n">
         <v>120</v>
       </c>
@@ -8661,8 +8252,6 @@
           <t>Monroeville, PA</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
         <v>8</v>
       </c>
@@ -8679,7 +8268,6 @@
       <c r="I140" t="n">
         <v>58</v>
       </c>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="n">
         <v>120</v>
       </c>
@@ -8720,8 +8308,6 @@
           <t>Bradford, PA</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
         <v>2</v>
       </c>
@@ -8738,7 +8324,6 @@
       <c r="I141" t="n">
         <v>5</v>
       </c>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="n">
         <v>120</v>
       </c>
@@ -8806,8 +8391,6 @@
       <c r="J142" t="n">
         <v>22</v>
       </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
           <t>64</t>
@@ -8867,8 +8450,6 @@
       <c r="J143" t="n">
         <v>28</v>
       </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
           <t>62</t>
@@ -8928,8 +8509,6 @@
       <c r="J144" t="n">
         <v>35</v>
       </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
           <t>58</t>
@@ -8989,8 +8568,6 @@
       <c r="J145" t="n">
         <v>20</v>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>64</t>
@@ -9050,8 +8627,6 @@
       <c r="J146" t="n">
         <v>18</v>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>60</t>
@@ -9111,8 +8686,6 @@
       <c r="J147" t="n">
         <v>40</v>
       </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>62</t>
@@ -9172,8 +8745,6 @@
       <c r="J148" t="n">
         <v>30</v>
       </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
           <t>60</t>
@@ -9233,8 +8804,6 @@
       <c r="J149" t="n">
         <v>25</v>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>62</t>
@@ -9294,8 +8863,6 @@
       <c r="J150" t="n">
         <v>15</v>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>73</t>
@@ -9355,8 +8922,6 @@
       <c r="J151" t="n">
         <v>22</v>
       </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>78</t>
@@ -9389,8 +8954,6 @@
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
         <v>2</v>
       </c>
@@ -9404,8 +8967,6 @@
           <t>Condo</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="n">
         <v>5</v>
       </c>
@@ -9446,8 +9007,6 @@
           <t>West Chester, PA</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
         <v>1</v>
       </c>
@@ -9461,8 +9020,6 @@
           <t>Condo</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="n">
         <v>4</v>
       </c>
@@ -9503,8 +9060,6 @@
           <t>Coatesville, PA</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
         <v>2</v>
       </c>
@@ -9518,8 +9073,6 @@
           <t>Condo</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="n">
         <v>9</v>
       </c>
@@ -9560,8 +9113,6 @@
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
         <v>3</v>
       </c>
@@ -9575,8 +9126,6 @@
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="n">
         <v>7</v>
       </c>
@@ -9617,8 +9166,6 @@
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>2</v>
       </c>
@@ -9632,8 +9179,6 @@
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="n">
         <v>6</v>
       </c>
@@ -9674,8 +9219,6 @@
           <t>Stroudsburg, PA</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>4</v>
       </c>
@@ -9689,8 +9232,6 @@
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="n">
         <v>11</v>
       </c>
@@ -9731,8 +9272,6 @@
           <t>Levittown, PA</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>1</v>
       </c>
@@ -9746,8 +9285,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="n">
         <v>3</v>
       </c>
@@ -9788,8 +9325,6 @@
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>2</v>
       </c>
@@ -9803,8 +9338,6 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="n">
         <v>5</v>
       </c>
@@ -9845,8 +9378,6 @@
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>1</v>
       </c>
@@ -9860,8 +9391,6 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="n">
         <v>6</v>
       </c>
@@ -9902,8 +9431,6 @@
           <t>Quakertown, PA</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>2</v>
       </c>
@@ -9917,8 +9444,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="n">
         <v>4</v>
       </c>
@@ -9959,8 +9484,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>2</v>
       </c>
@@ -9974,8 +9497,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="n">
         <v>5</v>
       </c>
@@ -10016,8 +9537,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>2</v>
       </c>
@@ -10031,8 +9550,6 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="n">
         <v>32</v>
       </c>
@@ -10073,8 +9590,6 @@
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
       </c>
@@ -10091,7 +9606,6 @@
       <c r="I164" t="n">
         <v>62</v>
       </c>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="n">
         <v>120</v>
       </c>
@@ -10132,8 +9646,6 @@
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
         <v>2</v>
       </c>
@@ -10150,7 +9662,6 @@
       <c r="I165" t="n">
         <v>75</v>
       </c>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="n">
         <v>115</v>
       </c>
@@ -10191,8 +9702,6 @@
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="n">
         <v>4</v>
       </c>
@@ -10209,7 +9718,6 @@
       <c r="I166" t="n">
         <v>55</v>
       </c>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="n">
         <v>120</v>
       </c>
@@ -10250,8 +9758,6 @@
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="n">
         <v>2</v>
       </c>
@@ -10268,7 +9774,6 @@
       <c r="I167" t="n">
         <v>62</v>
       </c>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="n">
         <v>115</v>
       </c>
@@ -10309,8 +9814,6 @@
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
         <v>3</v>
       </c>
@@ -10327,7 +9830,6 @@
       <c r="I168" t="n">
         <v>48</v>
       </c>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="n">
         <v>120</v>
       </c>
@@ -10368,8 +9870,6 @@
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
         <v>4</v>
       </c>
@@ -10386,7 +9886,6 @@
       <c r="I169" t="n">
         <v>70</v>
       </c>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="n">
         <v>120</v>
       </c>
@@ -10427,8 +9926,6 @@
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
         <v>1</v>
       </c>
@@ -10445,7 +9942,6 @@
       <c r="I170" t="n">
         <v>38</v>
       </c>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="n">
         <v>105</v>
       </c>
@@ -10486,8 +9982,6 @@
           <t>New Castle, PA</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
         <v>1</v>
       </c>
@@ -10504,7 +9998,6 @@
       <c r="I171" t="n">
         <v>45</v>
       </c>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="n">
         <v>110</v>
       </c>
@@ -10545,8 +10038,6 @@
           <t>Uniontown, PA</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>2</v>
       </c>
@@ -10563,7 +10054,6 @@
       <c r="I172" t="n">
         <v>52</v>
       </c>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="n">
         <v>115</v>
       </c>
@@ -10604,8 +10094,6 @@
           <t>Williamsport, PA</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
         <v>3</v>
       </c>
@@ -10622,7 +10110,6 @@
       <c r="I173" t="n">
         <v>48</v>
       </c>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="n">
         <v>120</v>
       </c>
@@ -10663,8 +10150,6 @@
           <t>Williamsport, PA</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
         <v>2</v>
       </c>
@@ -10681,7 +10166,6 @@
       <c r="I174" t="n">
         <v>35</v>
       </c>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="n">
         <v>120</v>
       </c>
@@ -10722,8 +10206,6 @@
           <t>West Mifflin, PA</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -10740,7 +10222,6 @@
       <c r="I175" t="n">
         <v>60</v>
       </c>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="n">
         <v>120</v>
       </c>
@@ -10781,8 +10262,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>2</v>
       </c>
@@ -10799,7 +10278,6 @@
       <c r="I176" t="n">
         <v>42</v>
       </c>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="n">
         <v>120</v>
       </c>
@@ -10840,8 +10318,6 @@
           <t>Uniontown, PA</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>7</v>
       </c>
@@ -10858,8 +10334,6 @@
       <c r="I177" t="n">
         <v>58</v>
       </c>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -10897,8 +10371,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -10915,8 +10387,6 @@
       <c r="I178" t="n">
         <v>10</v>
       </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -10954,8 +10424,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>2</v>
       </c>
@@ -10972,8 +10440,6 @@
       <c r="I179" t="n">
         <v>20</v>
       </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>2</t>
@@ -11011,8 +10477,6 @@
           <t>Stroudsburg, PA</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -11029,8 +10493,6 @@
       <c r="I180" t="n">
         <v>32</v>
       </c>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -11068,8 +10530,6 @@
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>2</v>
       </c>
@@ -11086,8 +10546,6 @@
       <c r="I181" t="n">
         <v>75</v>
       </c>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>2</t>
@@ -11125,8 +10583,6 @@
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -11143,8 +10599,6 @@
       <c r="I182" t="n">
         <v>92</v>
       </c>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -11209,8 +10663,6 @@
       <c r="J183" t="n">
         <v>27</v>
       </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
           <t>72</t>
@@ -11270,8 +10722,6 @@
       <c r="J184" t="n">
         <v>27</v>
       </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
           <t>68</t>
@@ -11331,8 +10781,6 @@
       <c r="J185" t="n">
         <v>48</v>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
           <t>74</t>
@@ -11392,8 +10840,6 @@
       <c r="J186" t="n">
         <v>32</v>
       </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
           <t>78</t>

--- a/Scenario Files/TestScenarios.xlsx
+++ b/Scenario Files/TestScenarios.xlsx
@@ -6421,7 +6421,7 @@
         <v>28</v>
       </c>
       <c r="K107" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>75</v>
       </c>
       <c r="K108" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>78</v>
       </c>
       <c r="K109" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>28</v>
       </c>
       <c r="K110" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>32</v>
       </c>
       <c r="K111" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>30</v>
       </c>
       <c r="K112" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>82</v>
       </c>
       <c r="K113" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>30</v>
       </c>
       <c r="K115" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>85</v>
       </c>
       <c r="K116" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>15</v>
       </c>
       <c r="K117" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>78</v>
       </c>
       <c r="K118" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>88</v>
       </c>
       <c r="K119" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>22</v>
       </c>
       <c r="K120" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>30</v>
       </c>
       <c r="K121" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>55</v>
       </c>
       <c r="K122" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>58</v>
       </c>
       <c r="K123" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>65</v>
       </c>
       <c r="K124" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>50</v>
       </c>
       <c r="K125" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>72</v>
       </c>
       <c r="K126" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>52</v>
       </c>
       <c r="K127" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45</v>
       </c>
       <c r="K128" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>55</v>
       </c>
       <c r="K129" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>55</v>
       </c>
       <c r="K130" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>60</v>
       </c>
       <c r="K131" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>92</v>
       </c>
       <c r="K132" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>42</v>
       </c>
       <c r="K133" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>38</v>
       </c>
       <c r="K134" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>55</v>
       </c>
       <c r="K135" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>62</v>
       </c>
       <c r="K136" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>50</v>
       </c>
       <c r="K137" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>58</v>
       </c>
       <c r="K138" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>55</v>
       </c>
       <c r="K139" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>58</v>
       </c>
       <c r="K140" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>5</v>
       </c>
       <c r="K141" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>62</v>
       </c>
       <c r="K164" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>75</v>
       </c>
       <c r="K165" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>55</v>
       </c>
       <c r="K166" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>62</v>
       </c>
       <c r="K167" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>48</v>
       </c>
       <c r="K168" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>70</v>
       </c>
       <c r="K169" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>38</v>
       </c>
       <c r="K170" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45</v>
       </c>
       <c r="K171" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>52</v>
       </c>
       <c r="K172" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>48</v>
       </c>
       <c r="K173" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>35</v>
       </c>
       <c r="K174" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>60</v>
       </c>
       <c r="K175" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>42</v>
       </c>
       <c r="K176" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>

--- a/Scenario Files/TestScenarios.xlsx
+++ b/Scenario Files/TestScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,17 +419,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Decision Type</t>
+          <t>decision_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Insulation</t>
+          <t>insulation</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -449,12 +449,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Utility Budget</t>
+          <t>utility_budget</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Housing Type</t>
+          <t>housing_type</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -469,27 +469,27 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Appliance Age</t>
+          <t>appliance_age</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Flow rate</t>
+          <t>flow_rate</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Alternative 1</t>
+          <t>alternative_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Alternative 2</t>
+          <t>alternative_2</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Alternative 3</t>
+          <t>alternative_3</t>
         </is>
       </c>
     </row>
@@ -534,8 +534,6 @@
       <c r="J2" t="n">
         <v>20</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>72</v>
       </c>
@@ -589,8 +587,6 @@
       <c r="J3" t="n">
         <v>20</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>68</v>
       </c>
@@ -644,8 +640,6 @@
       <c r="J4" t="n">
         <v>30</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>77</v>
       </c>
@@ -699,8 +693,6 @@
       <c r="J5" t="n">
         <v>30</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>65</v>
       </c>
@@ -754,8 +746,6 @@
       <c r="J6" t="n">
         <v>35</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>74</v>
       </c>
@@ -809,8 +799,6 @@
       <c r="J7" t="n">
         <v>40</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>78</v>
       </c>
@@ -864,8 +852,6 @@
       <c r="J8" t="n">
         <v>40</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>64</v>
       </c>
@@ -919,8 +905,6 @@
       <c r="J9" t="n">
         <v>23</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>76</v>
       </c>
@@ -974,8 +958,6 @@
       <c r="J10" t="n">
         <v>23</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>67</v>
       </c>
@@ -1029,8 +1011,6 @@
       <c r="J11" t="n">
         <v>12</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>68</v>
       </c>
@@ -1084,8 +1064,6 @@
       <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>76</v>
       </c>
@@ -1139,8 +1117,6 @@
       <c r="J13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>66</v>
       </c>
@@ -1194,8 +1170,6 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>76</v>
       </c>
@@ -1249,8 +1223,6 @@
       <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>73</v>
       </c>
@@ -1304,8 +1276,6 @@
       <c r="J16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>78</v>
       </c>
@@ -1359,8 +1329,6 @@
       <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>65</v>
       </c>
@@ -1414,8 +1382,6 @@
       <c r="J18" t="n">
         <v>7</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>75</v>
       </c>
@@ -1469,8 +1435,6 @@
       <c r="J19" t="n">
         <v>9</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>78</v>
       </c>
@@ -1524,8 +1488,6 @@
       <c r="J20" t="n">
         <v>11</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>71</v>
       </c>
@@ -1579,8 +1541,6 @@
       <c r="J21" t="n">
         <v>12</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>66</v>
       </c>
@@ -1634,8 +1594,6 @@
       <c r="J22" t="n">
         <v>16</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>65</v>
       </c>
@@ -1689,8 +1647,6 @@
       <c r="J23" t="n">
         <v>19</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>75</v>
       </c>
@@ -1744,8 +1700,6 @@
       <c r="J24" t="n">
         <v>19</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>66</v>
       </c>
@@ -1799,8 +1753,6 @@
       <c r="J25" t="n">
         <v>25</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>78</v>
       </c>
@@ -1854,8 +1806,6 @@
       <c r="J26" t="n">
         <v>26</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>76</v>
       </c>
@@ -1909,8 +1859,6 @@
       <c r="J27" t="n">
         <v>30</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>66</v>
       </c>
@@ -1964,8 +1912,6 @@
       <c r="J28" t="n">
         <v>95</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>66</v>
       </c>
@@ -2019,8 +1965,6 @@
       <c r="J29" t="n">
         <v>35</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>78</v>
       </c>
@@ -2074,8 +2018,6 @@
       <c r="J30" t="n">
         <v>30</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>79</v>
       </c>
@@ -2129,8 +2071,6 @@
       <c r="J31" t="n">
         <v>18</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>77</v>
       </c>
@@ -2184,8 +2124,6 @@
       <c r="J32" t="n">
         <v>8</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>82</v>
       </c>
@@ -2239,8 +2177,6 @@
       <c r="J33" t="n">
         <v>25</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>78</v>
       </c>
@@ -2294,8 +2230,6 @@
       <c r="J34" t="n">
         <v>28</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>79</v>
       </c>
@@ -2349,8 +2283,6 @@
       <c r="J35" t="n">
         <v>28</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>78</v>
       </c>
@@ -2404,8 +2336,6 @@
       <c r="J36" t="n">
         <v>25</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>60</v>
       </c>
@@ -2459,8 +2389,6 @@
       <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>73</v>
       </c>
@@ -2514,8 +2442,6 @@
       <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>74</v>
       </c>
@@ -2569,8 +2495,6 @@
       <c r="J39" t="n">
         <v>16</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>66</v>
       </c>
@@ -2624,8 +2548,6 @@
       <c r="J40" t="n">
         <v>25</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>65</v>
       </c>
@@ -2679,8 +2601,6 @@
       <c r="J41" t="n">
         <v>18</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>66</v>
       </c>
@@ -2734,8 +2654,6 @@
       <c r="J42" t="n">
         <v>18</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>71</v>
       </c>
@@ -2789,8 +2707,6 @@
       <c r="J43" t="n">
         <v>32</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>65</v>
       </c>
@@ -2844,8 +2760,6 @@
       <c r="J44" t="n">
         <v>18</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>78</v>
       </c>
@@ -2899,8 +2813,6 @@
       <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>78</v>
       </c>
@@ -2954,8 +2866,6 @@
       <c r="J46" t="n">
         <v>6</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>73</v>
       </c>
@@ -3009,8 +2919,6 @@
       <c r="J47" t="n">
         <v>16</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>65</v>
       </c>
@@ -3064,8 +2972,6 @@
       <c r="J48" t="n">
         <v>20</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>66</v>
       </c>
@@ -3119,8 +3025,6 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>67</v>
       </c>
@@ -3174,8 +3078,6 @@
       <c r="J50" t="n">
         <v>3</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>66</v>
       </c>
@@ -3229,8 +3131,6 @@
       <c r="J51" t="n">
         <v>20</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>70</v>
       </c>
@@ -3284,8 +3184,6 @@
       <c r="J52" t="n">
         <v>33</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
         <v>74</v>
       </c>
@@ -3339,8 +3237,6 @@
       <c r="J53" t="n">
         <v>8</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
         <v>68</v>
       </c>
@@ -3394,8 +3290,6 @@
       <c r="J54" t="n">
         <v>6</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
         <v>66</v>
       </c>
@@ -3449,8 +3343,6 @@
       <c r="J55" t="n">
         <v>11</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
         <v>65</v>
       </c>
@@ -3504,8 +3396,6 @@
       <c r="J56" t="n">
         <v>3</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>66</v>
       </c>
@@ -3559,8 +3449,6 @@
       <c r="J57" t="n">
         <v>7</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
         <v>72</v>
       </c>
@@ -3614,8 +3502,6 @@
       <c r="J58" t="n">
         <v>4</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>72</v>
       </c>
@@ -3669,8 +3555,6 @@
       <c r="J59" t="n">
         <v>21</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>73</v>
       </c>
@@ -3724,8 +3608,6 @@
       <c r="J60" t="n">
         <v>15</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
         <v>62</v>
       </c>
@@ -3779,8 +3661,6 @@
       <c r="J61" t="n">
         <v>6</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>66</v>
       </c>
@@ -3834,8 +3714,6 @@
       <c r="J62" t="n">
         <v>18</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>64</v>
       </c>
@@ -3889,8 +3767,6 @@
       <c r="J63" t="n">
         <v>24</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
         <v>62</v>
       </c>
@@ -3944,8 +3820,6 @@
       <c r="J64" t="n">
         <v>28</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>58</v>
       </c>
@@ -3999,8 +3873,6 @@
       <c r="J65" t="n">
         <v>16</v>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
         <v>64</v>
       </c>
@@ -4054,8 +3926,6 @@
       <c r="J66" t="n">
         <v>14</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
         <v>60</v>
       </c>
@@ -4109,8 +3979,6 @@
       <c r="J67" t="n">
         <v>32</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
         <v>62</v>
       </c>
@@ -4164,8 +4032,6 @@
       <c r="J68" t="n">
         <v>22</v>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>60</v>
       </c>
@@ -4219,8 +4085,6 @@
       <c r="J69" t="n">
         <v>20</v>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
         <v>62</v>
       </c>
@@ -4274,8 +4138,6 @@
       <c r="J70" t="n">
         <v>12</v>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>73</v>
       </c>
@@ -4329,8 +4191,6 @@
       <c r="J71" t="n">
         <v>18</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>78</v>
       </c>
@@ -4359,8 +4219,6 @@
           <t>Monroeville, PA</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
         <v>3</v>
       </c>
@@ -4372,12 +4230,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
         <v>8</v>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -4410,8 +4265,6 @@
           <t>Indiana, PA</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
         <v>4</v>
       </c>
@@ -4423,12 +4276,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
         <v>12</v>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -4461,8 +4311,6 @@
           <t>Uniontown, PA</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
         <v>5</v>
       </c>
@@ -4474,12 +4322,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
         <v>6</v>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -4512,8 +4357,6 @@
           <t>Butler, PA</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
         <v>3</v>
       </c>
@@ -4525,12 +4368,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
         <v>3</v>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -4555,7 +4395,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>It's just past 5 PM � when should I run the dryer?</t>
+          <t>It's just past 5 PM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4563,8 +4403,6 @@
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
         <v>2</v>
       </c>
@@ -4576,12 +4414,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
         <v>15</v>
       </c>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -4614,8 +4449,6 @@
           <t>Monroeville, PA</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>5</v>
       </c>
@@ -4627,12 +4460,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
         <v>10</v>
       </c>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -4665,8 +4495,6 @@
           <t>Indiana, PA</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>4</v>
       </c>
@@ -4678,12 +4506,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
         <v>7</v>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -4716,8 +4541,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>4</v>
       </c>
@@ -4729,12 +4552,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
         <v>7</v>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -4767,8 +4587,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
       </c>
@@ -4780,12 +4598,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
         <v>10</v>
       </c>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -4810,7 +4625,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>It's around 7 in the evening � when should I run the dishwasher?</t>
+          <t>It's around 7 in the evening — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4818,8 +4633,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
       </c>
@@ -4831,12 +4644,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
         <v>2</v>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -4869,8 +4679,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>4</v>
       </c>
@@ -4882,12 +4690,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
         <v>6</v>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -4920,8 +4725,6 @@
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
       </c>
@@ -4933,12 +4736,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
         <v>4</v>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -4971,8 +4771,6 @@
           <t>West Chester, PA</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>4</v>
       </c>
@@ -4984,12 +4782,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
         <v>6</v>
       </c>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -5022,8 +4817,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
       </c>
@@ -5035,12 +4828,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="n">
         <v>12</v>
       </c>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -5073,8 +4863,6 @@
           <t>DuBois, PA</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>5</v>
       </c>
@@ -5086,12 +4874,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
         <v>8</v>
       </c>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -5116,7 +4901,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>It's getting close to midnight � when should I run the washing machine?</t>
+          <t>It's getting close to midnight — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5124,8 +4909,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
         <v>5</v>
       </c>
@@ -5137,12 +4920,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
         <v>6</v>
       </c>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -5167,7 +4947,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>It's just past 5 PM � when should I run the washer?</t>
+          <t>It's just past 5 PM — when should I run the washer?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5175,8 +4955,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
         <v>3</v>
       </c>
@@ -5188,12 +4966,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
         <v>10</v>
       </c>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -5226,8 +5001,6 @@
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
         <v>3</v>
       </c>
@@ -5239,12 +5012,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
         <v>12</v>
       </c>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -5277,8 +5047,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
         <v>4</v>
       </c>
@@ -5290,12 +5058,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="n">
         <v>7</v>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -5328,8 +5093,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
         <v>2</v>
       </c>
@@ -5341,12 +5104,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
         <v>15</v>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -5379,8 +5139,6 @@
           <t>Carlisle, PA</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
         <v>3</v>
       </c>
@@ -5392,12 +5150,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
         <v>2</v>
       </c>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -5430,8 +5185,6 @@
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
         <v>5</v>
       </c>
@@ -5443,12 +5196,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="n">
         <v>4</v>
       </c>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -5481,8 +5231,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
         <v>4</v>
       </c>
@@ -5494,12 +5242,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
         <v>15</v>
       </c>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -5532,8 +5277,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
         <v>4</v>
       </c>
@@ -5545,12 +5288,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
         <v>6</v>
       </c>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -5575,7 +5315,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>It's past 1 in the morning � when should I run the dryer?</t>
+          <t>It's past 1 in the morning — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5583,8 +5323,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
         <v>4</v>
       </c>
@@ -5596,12 +5334,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
         <v>12</v>
       </c>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -5634,8 +5369,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
         <v>3</v>
       </c>
@@ -5647,12 +5380,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
         <v>8</v>
       </c>
-      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -5685,8 +5415,6 @@
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
         <v>3</v>
       </c>
@@ -5698,12 +5426,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
         <v>10</v>
       </c>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -5736,8 +5461,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="n">
         <v>4</v>
       </c>
@@ -5749,12 +5472,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
         <v>3</v>
       </c>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -5779,7 +5499,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>It's just past midnight � when should I run the dishwasher?</t>
+          <t>It's just past midnight — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5787,8 +5507,6 @@
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
         <v>2</v>
       </c>
@@ -5800,12 +5518,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
         <v>12</v>
       </c>
-      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -5838,8 +5553,6 @@
           <t>Oil City, PA</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
         <v>2</v>
       </c>
@@ -5851,12 +5564,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
         <v>15</v>
       </c>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -5889,8 +5599,6 @@
           <t>Gettysburg, PA</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
         <v>2</v>
       </c>
@@ -5902,12 +5610,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
         <v>2</v>
       </c>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -5940,8 +5645,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
         <v>2</v>
       </c>
@@ -5953,12 +5656,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
         <v>5</v>
       </c>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -5991,8 +5691,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
         <v>3</v>
       </c>
@@ -6004,12 +5702,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
         <v>6</v>
       </c>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -6034,7 +5729,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>It's around 8 at night � when should I run the dishwasher?</t>
+          <t>It's around 8 at night — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6042,8 +5737,6 @@
           <t>Media, PA</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
         <v>4</v>
       </c>
@@ -6055,12 +5748,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
         <v>4</v>
       </c>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -6093,8 +5783,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
         <v>2</v>
       </c>
@@ -6106,12 +5794,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
         <v>10</v>
       </c>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -6144,8 +5829,6 @@
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
         <v>2</v>
       </c>
@@ -6157,12 +5840,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
         <v>2</v>
       </c>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>7:00 AM</t>
@@ -6195,8 +5875,6 @@
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
         <v>4</v>
       </c>
@@ -6208,12 +5886,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
         <v>8</v>
       </c>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -6246,8 +5921,6 @@
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
         <v>3</v>
       </c>
@@ -6259,12 +5932,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
         <v>10</v>
       </c>
-      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
           <t>7:00 AM</t>
@@ -6297,8 +5967,6 @@
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
         <v>5</v>
       </c>
@@ -6310,12 +5978,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
         <v>6</v>
       </c>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -6348,8 +6013,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
         <v>2</v>
       </c>
@@ -6361,12 +6024,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
         <v>10</v>
       </c>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>9:00 AM</t>
@@ -6399,8 +6059,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
         <v>3</v>
       </c>
@@ -6412,12 +6070,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
         <v>5</v>
       </c>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -6450,8 +6105,6 @@
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
         <v>3</v>
       </c>
@@ -6463,12 +6116,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
         <v>4</v>
       </c>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -6501,8 +6151,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
         <v>2</v>
       </c>
@@ -6514,12 +6162,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="n">
         <v>5</v>
       </c>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -6552,8 +6197,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
         <v>4</v>
       </c>
@@ -6565,12 +6208,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="n">
         <v>4</v>
       </c>
-      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -6603,8 +6243,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
         <v>3</v>
       </c>
@@ -6616,12 +6254,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
         <v>8</v>
       </c>
-      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -6654,8 +6289,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
         <v>2</v>
       </c>
@@ -6667,12 +6300,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
         <v>3</v>
       </c>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>2:00 PM</t>
@@ -6705,8 +6335,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
         <v>4</v>
       </c>
@@ -6718,12 +6346,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="n">
         <v>15</v>
       </c>
-      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -6756,8 +6381,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
         <v>3</v>
       </c>
@@ -6769,12 +6392,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
         <v>5</v>
       </c>
-      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
           <t>11:00 PM</t>
@@ -6807,8 +6427,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
         <v>2</v>
       </c>
@@ -6820,12 +6438,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
         <v>4</v>
       </c>
-      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
           <t>12:00 AM</t>
@@ -6858,8 +6473,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
         <v>2</v>
       </c>
@@ -6871,12 +6484,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
         <v>8</v>
       </c>
-      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
           <t>1:00 AM</t>
@@ -6909,8 +6519,6 @@
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
         <v>5</v>
       </c>
@@ -6922,12 +6530,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="n">
         <v>4</v>
       </c>
-      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -6960,8 +6565,6 @@
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>5</v>
       </c>
@@ -6973,12 +6576,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="n">
         <v>5</v>
       </c>
-      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>3:00 AM</t>
@@ -7011,8 +6611,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>5</v>
       </c>
@@ -7024,12 +6622,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
         <v>3</v>
       </c>
-      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>8:00 PM</t>
@@ -7062,8 +6657,6 @@
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>4</v>
       </c>
@@ -7075,12 +6668,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="n">
         <v>8</v>
       </c>
-      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
           <t>4:00 PM</t>
@@ -7113,8 +6703,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>2</v>
       </c>
@@ -7126,12 +6714,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="n">
         <v>32</v>
       </c>
-      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
           <t>5:00 PM</t>
@@ -7164,8 +6749,6 @@
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>2</v>
       </c>
@@ -7177,12 +6760,9 @@
           <t>Condo</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
         <v>5</v>
       </c>
-      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
           <t>9:00 AM</t>
@@ -7215,8 +6795,6 @@
           <t>West Chester, PA</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
         <v>1</v>
       </c>
@@ -7228,12 +6806,9 @@
           <t>Condo</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
         <v>4</v>
       </c>
-      <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
           <t>6:00 PM</t>
@@ -7266,8 +6841,6 @@
           <t>Coatesville, PA</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
         <v>2</v>
       </c>
@@ -7279,12 +6852,9 @@
           <t>Condo</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="n">
         <v>9</v>
       </c>
-      <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
           <t>10:00 AM</t>
@@ -7317,8 +6887,6 @@
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
         <v>3</v>
       </c>
@@ -7330,12 +6898,9 @@
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="n">
         <v>7</v>
       </c>
-      <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -7368,8 +6933,6 @@
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
         <v>2</v>
       </c>
@@ -7381,12 +6944,9 @@
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
         <v>6</v>
       </c>
-      <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -7419,8 +6979,6 @@
           <t>Stroudsburg, PA</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
         <v>4</v>
       </c>
@@ -7432,12 +6990,9 @@
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
         <v>11</v>
       </c>
-      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -7470,8 +7025,6 @@
           <t>Levittown, PA</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="n">
         <v>1</v>
       </c>
@@ -7483,12 +7036,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="n">
         <v>3</v>
       </c>
-      <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
           <t>8:00 AM</t>
@@ -7521,8 +7071,6 @@
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
         <v>2</v>
       </c>
@@ -7534,12 +7082,9 @@
           <t>Single-family</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="n">
         <v>5</v>
       </c>
-      <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
           <t>3:00 PM</t>
@@ -7572,8 +7117,6 @@
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="n">
         <v>1</v>
       </c>
@@ -7585,12 +7128,9 @@
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="n">
         <v>6</v>
       </c>
-      <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
           <t>7:00 PM</t>
@@ -7623,8 +7163,6 @@
           <t>Quakertown, PA</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>2</v>
       </c>
@@ -7636,12 +7174,9 @@
           <t>Apartment</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
         <v>4</v>
       </c>
-      <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
           <t>11:00 AM</t>
@@ -7674,8 +7209,6 @@
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
         <v>2</v>
       </c>
@@ -7690,8 +7223,6 @@
       <c r="I137" t="n">
         <v>28</v>
       </c>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
       <c r="L137" t="n">
         <v>1.5</v>
       </c>
@@ -7721,8 +7252,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>3</v>
       </c>
@@ -7737,8 +7266,6 @@
       <c r="I138" t="n">
         <v>85</v>
       </c>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
         <v>1.5</v>
       </c>
@@ -7768,8 +7295,6 @@
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>1</v>
       </c>
@@ -7784,8 +7309,6 @@
       <c r="I139" t="n">
         <v>18</v>
       </c>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
         <v>1.5</v>
       </c>
@@ -7815,8 +7338,6 @@
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
         <v>2</v>
       </c>
@@ -7831,8 +7352,6 @@
       <c r="I140" t="n">
         <v>75</v>
       </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
       <c r="L140" t="n">
         <v>2.5</v>
       </c>
@@ -7862,8 +7381,6 @@
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
         <v>4</v>
       </c>
@@ -7878,8 +7395,6 @@
       <c r="I141" t="n">
         <v>78</v>
       </c>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
       <c r="L141" t="n">
         <v>1.5</v>
       </c>
@@ -7909,8 +7424,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
         <v>4</v>
       </c>
@@ -7925,8 +7438,6 @@
       <c r="I142" t="n">
         <v>28</v>
       </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
         <v>2.5</v>
       </c>
@@ -7956,8 +7467,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>2</v>
       </c>
@@ -7972,8 +7481,6 @@
       <c r="I143" t="n">
         <v>32</v>
       </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
         <v>1.5</v>
       </c>
@@ -8003,8 +7510,6 @@
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
         <v>5</v>
       </c>
@@ -8019,8 +7524,6 @@
       <c r="I144" t="n">
         <v>30</v>
       </c>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
       <c r="L144" t="n">
         <v>1.5</v>
       </c>
@@ -8050,8 +7553,6 @@
           <t>Reading, PA</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
         <v>5</v>
       </c>
@@ -8066,8 +7567,6 @@
       <c r="I145" t="n">
         <v>82</v>
       </c>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="n">
         <v>2.5</v>
       </c>
@@ -8097,8 +7596,6 @@
           <t>York, PA</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
         <v>5</v>
       </c>
@@ -8113,8 +7610,6 @@
       <c r="I146" t="n">
         <v>20</v>
       </c>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
       <c r="L146" t="n">
         <v>3.5</v>
       </c>
@@ -8144,8 +7639,6 @@
           <t>West Chester, PA</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
         <v>6</v>
       </c>
@@ -8160,8 +7653,6 @@
       <c r="I147" t="n">
         <v>82</v>
       </c>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
         <v>3.5</v>
       </c>
@@ -8191,8 +7682,6 @@
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
         <v>4</v>
       </c>
@@ -8207,8 +7696,6 @@
       <c r="I148" t="n">
         <v>30</v>
       </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="n">
         <v>2.5</v>
       </c>
@@ -8238,8 +7725,6 @@
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="n">
         <v>3</v>
       </c>
@@ -8254,8 +7739,6 @@
       <c r="I149" t="n">
         <v>85</v>
       </c>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
         <v>2.5</v>
       </c>
@@ -8285,8 +7768,6 @@
           <t>Media, PA</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
         <v>4</v>
       </c>
@@ -8301,8 +7782,6 @@
       <c r="I150" t="n">
         <v>25</v>
       </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
       <c r="L150" t="n">
         <v>3.5</v>
       </c>
@@ -8332,8 +7811,6 @@
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="n">
         <v>3</v>
       </c>
@@ -8348,8 +7825,6 @@
       <c r="I151" t="n">
         <v>90</v>
       </c>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
       <c r="L151" t="n">
         <v>3.5</v>
       </c>
@@ -8379,8 +7854,6 @@
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
         <v>6</v>
       </c>
@@ -8395,8 +7868,6 @@
       <c r="I152" t="n">
         <v>15</v>
       </c>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
       <c r="L152" t="n">
         <v>4</v>
       </c>
@@ -8426,8 +7897,6 @@
           <t>Pottstown, PA</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="n">
         <v>2</v>
       </c>
@@ -8442,8 +7911,6 @@
       <c r="I153" t="n">
         <v>78</v>
       </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" t="n">
         <v>2</v>
       </c>
@@ -8473,8 +7940,6 @@
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="n">
         <v>5</v>
       </c>
@@ -8489,8 +7954,6 @@
       <c r="I154" t="n">
         <v>88</v>
       </c>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
       <c r="L154" t="n">
         <v>4</v>
       </c>
@@ -8520,8 +7983,6 @@
           <t>Newtown, PA</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="n">
         <v>4</v>
       </c>
@@ -8536,8 +7997,6 @@
       <c r="I155" t="n">
         <v>22</v>
       </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
       <c r="L155" t="n">
         <v>2</v>
       </c>
@@ -8567,8 +8026,6 @@
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>5</v>
       </c>
@@ -8583,8 +8040,6 @@
       <c r="I156" t="n">
         <v>80</v>
       </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" t="n">
         <v>2.5</v>
       </c>
@@ -8614,8 +8069,6 @@
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
         <v>7</v>
       </c>
@@ -8630,8 +8083,6 @@
       <c r="I157" t="n">
         <v>12</v>
       </c>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
       <c r="L157" t="n">
         <v>3</v>
       </c>
@@ -8661,8 +8112,6 @@
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>2</v>
       </c>
@@ -8677,8 +8126,6 @@
       <c r="I158" t="n">
         <v>92</v>
       </c>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
       <c r="L158" t="n">
         <v>2</v>
       </c>
@@ -8708,8 +8155,6 @@
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>3</v>
       </c>
@@ -8724,8 +8169,6 @@
       <c r="I159" t="n">
         <v>30</v>
       </c>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
       <c r="L159" t="n">
         <v>3.5</v>
       </c>
@@ -8755,8 +8198,6 @@
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>2</v>
       </c>
@@ -8771,8 +8212,6 @@
       <c r="I160" t="n">
         <v>70</v>
       </c>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
       <c r="L160" t="n">
         <v>3.5</v>
       </c>
@@ -8802,8 +8241,6 @@
           <t>Chambersburg, PA</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>4</v>
       </c>
@@ -8818,8 +8255,6 @@
       <c r="I161" t="n">
         <v>55</v>
       </c>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
         <v>4</v>
       </c>
@@ -8849,8 +8284,6 @@
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>4</v>
       </c>
@@ -8865,8 +8298,6 @@
       <c r="I162" t="n">
         <v>58</v>
       </c>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
       <c r="L162" t="n">
         <v>2</v>
       </c>
@@ -8896,8 +8327,6 @@
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>2</v>
       </c>
@@ -8912,8 +8341,6 @@
       <c r="I163" t="n">
         <v>65</v>
       </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
       <c r="L163" t="n">
         <v>2.5</v>
       </c>
@@ -8943,8 +8370,6 @@
           <t>Monroeville, PA</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>4</v>
       </c>
@@ -8959,8 +8384,6 @@
       <c r="I164" t="n">
         <v>50</v>
       </c>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
       <c r="L164" t="n">
         <v>2</v>
       </c>
@@ -8990,8 +8413,6 @@
           <t>Stroudsburg, PA</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
         <v>2</v>
       </c>
@@ -9006,8 +8427,6 @@
       <c r="I165" t="n">
         <v>40</v>
       </c>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
       <c r="L165" t="n">
         <v>2.5</v>
       </c>
@@ -9037,8 +8456,6 @@
           <t>Carlisle, PA</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="n">
         <v>3</v>
       </c>
@@ -9053,8 +8470,6 @@
       <c r="I166" t="n">
         <v>72</v>
       </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
       <c r="L166" t="n">
         <v>2</v>
       </c>
@@ -9084,8 +8499,6 @@
           <t>Coatesville, PA</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="n">
         <v>2</v>
       </c>
@@ -9100,8 +8513,6 @@
       <c r="I167" t="n">
         <v>52</v>
       </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
       <c r="L167" t="n">
         <v>2</v>
       </c>
@@ -9131,8 +8542,6 @@
           <t>DuBois, PA</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
         <v>3</v>
       </c>
@@ -9147,8 +8556,6 @@
       <c r="I168" t="n">
         <v>45</v>
       </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
       <c r="L168" t="n">
         <v>2.5</v>
       </c>
@@ -9178,8 +8585,6 @@
           <t>Gettysburg, PA</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
         <v>2</v>
       </c>
@@ -9194,8 +8599,6 @@
       <c r="I169" t="n">
         <v>60</v>
       </c>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
       <c r="L169" t="n">
         <v>2</v>
       </c>
@@ -9225,8 +8628,6 @@
           <t>Chester, PA</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -9241,8 +8642,6 @@
       <c r="I170" t="n">
         <v>55</v>
       </c>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
       <c r="L170" t="n">
         <v>2.5</v>
       </c>
@@ -9272,8 +8671,6 @@
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
         <v>4</v>
       </c>
@@ -9288,8 +8685,6 @@
       <c r="I171" t="n">
         <v>48</v>
       </c>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
       <c r="L171" t="n">
         <v>2.5</v>
       </c>
@@ -9319,8 +8714,6 @@
           <t>Butler, PA</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>5</v>
       </c>
@@ -9335,8 +8728,6 @@
       <c r="I172" t="n">
         <v>55</v>
       </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
       <c r="L172" t="n">
         <v>2.5</v>
       </c>
@@ -9366,8 +8757,6 @@
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
         <v>4</v>
       </c>
@@ -9382,8 +8771,6 @@
       <c r="I173" t="n">
         <v>50</v>
       </c>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
       <c r="L173" t="n">
         <v>3</v>
       </c>
@@ -9413,8 +8800,6 @@
           <t>Indiana, PA</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
         <v>6</v>
       </c>
@@ -9429,8 +8814,6 @@
       <c r="I174" t="n">
         <v>60</v>
       </c>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
         <v>2.5</v>
       </c>
@@ -9460,8 +8843,6 @@
           <t>Oil City, PA</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>5</v>
       </c>
@@ -9476,8 +8857,6 @@
       <c r="I175" t="n">
         <v>55</v>
       </c>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
       <c r="L175" t="n">
         <v>2</v>
       </c>
@@ -9507,8 +8886,6 @@
           <t>Uniontown, PA</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>7</v>
       </c>
@@ -9523,8 +8900,6 @@
       <c r="I176" t="n">
         <v>58</v>
       </c>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
       <c r="L176" t="n">
         <v>2.5</v>
       </c>
@@ -9554,8 +8929,6 @@
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -9570,8 +8943,6 @@
       <c r="I177" t="n">
         <v>10</v>
       </c>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
       <c r="L177" t="n">
         <v>2.5</v>
       </c>
@@ -9601,8 +8972,6 @@
           <t>Scranton, PA</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>2</v>
       </c>
@@ -9617,8 +8986,6 @@
       <c r="I178" t="n">
         <v>20</v>
       </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
       <c r="L178" t="n">
         <v>2</v>
       </c>
@@ -9648,8 +9015,6 @@
           <t>Stroudsburg, PA</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -9664,8 +9029,6 @@
       <c r="I179" t="n">
         <v>32</v>
       </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
       <c r="L179" t="n">
         <v>2.5</v>
       </c>
@@ -9695,8 +9058,6 @@
           <t>Phoenixville, PA</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -9711,8 +9072,6 @@
       <c r="I180" t="n">
         <v>92</v>
       </c>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
       <c r="L180" t="n">
         <v>2.5</v>
       </c>
@@ -9742,8 +9101,6 @@
           <t>Carlisle, PA</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>2</v>
       </c>
@@ -9758,8 +9115,6 @@
       <c r="I181" t="n">
         <v>42</v>
       </c>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
       <c r="L181" t="n">
         <v>3</v>
       </c>
@@ -9789,8 +9144,6 @@
           <t>DuBois, PA</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>5</v>
       </c>
@@ -9805,8 +9158,6 @@
       <c r="I182" t="n">
         <v>38</v>
       </c>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
       <c r="L182" t="n">
         <v>4</v>
       </c>
@@ -9836,8 +9187,6 @@
           <t>Gettysburg, PA</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -9852,8 +9201,6 @@
       <c r="I183" t="n">
         <v>55</v>
       </c>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
         <v>2</v>
       </c>
@@ -9883,8 +9230,6 @@
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
         <v>2</v>
       </c>
@@ -9899,8 +9244,6 @@
       <c r="I184" t="n">
         <v>62</v>
       </c>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
       <c r="L184" t="n">
         <v>2.5</v>
       </c>
@@ -9930,8 +9273,6 @@
           <t>Butler, PA</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
         <v>3</v>
       </c>
@@ -9946,8 +9287,6 @@
       <c r="I185" t="n">
         <v>50</v>
       </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
       <c r="L185" t="n">
         <v>2</v>
       </c>
@@ -9977,8 +9316,6 @@
           <t>Hazleton, PA</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>2</v>
       </c>
@@ -9993,8 +9330,6 @@
       <c r="I186" t="n">
         <v>58</v>
       </c>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
       <c r="L186" t="n">
         <v>2.5</v>
       </c>
@@ -10024,8 +9359,6 @@
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>4</v>
       </c>
@@ -10040,8 +9373,6 @@
       <c r="I187" t="n">
         <v>55</v>
       </c>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
       <c r="L187" t="n">
         <v>2.5</v>
       </c>
@@ -10071,8 +9402,6 @@
           <t>Monroeville, PA</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" t="n">
         <v>8</v>
       </c>
@@ -10087,8 +9416,6 @@
       <c r="I188" t="n">
         <v>58</v>
       </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
       <c r="L188" t="n">
         <v>2.5</v>
       </c>
@@ -10118,8 +9445,6 @@
           <t>Bradford, PA</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
       <c r="F189" t="n">
         <v>2</v>
       </c>
@@ -10134,8 +9459,6 @@
       <c r="I189" t="n">
         <v>5</v>
       </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
       <c r="L189" t="n">
         <v>2</v>
       </c>
@@ -10165,8 +9488,6 @@
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
         <v>2</v>
       </c>
@@ -10181,8 +9502,6 @@
       <c r="I190" t="n">
         <v>65</v>
       </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
       <c r="L190" t="n">
         <v>2</v>
       </c>
@@ -10212,8 +9531,6 @@
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
         <v>3</v>
       </c>
@@ -10228,8 +9545,6 @@
       <c r="I191" t="n">
         <v>78</v>
       </c>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
       <c r="L191" t="n">
         <v>2.5</v>
       </c>
@@ -10259,8 +9574,6 @@
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="n">
         <v>3</v>
       </c>
@@ -10275,8 +9588,6 @@
       <c r="I192" t="n">
         <v>72</v>
       </c>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
       <c r="L192" t="n">
         <v>2.5</v>
       </c>
@@ -10306,8 +9617,6 @@
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="n">
         <v>2</v>
       </c>
@@ -10322,8 +9631,6 @@
       <c r="I193" t="n">
         <v>58</v>
       </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
       <c r="L193" t="n">
         <v>2</v>
       </c>
@@ -10353,8 +9660,6 @@
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
         <v>1</v>
       </c>
@@ -10369,8 +9674,6 @@
       <c r="I194" t="n">
         <v>35</v>
       </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
       <c r="L194" t="n">
         <v>1.5</v>
       </c>
@@ -10400,8 +9703,6 @@
           <t>New Castle, PA</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
         <v>1</v>
       </c>
@@ -10416,8 +9717,6 @@
       <c r="I195" t="n">
         <v>45</v>
       </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
       <c r="L195" t="n">
         <v>2</v>
       </c>
@@ -10447,8 +9746,6 @@
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
         <v>2</v>
       </c>
@@ -10463,8 +9760,6 @@
       <c r="I196" t="n">
         <v>42</v>
       </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
         <v>2</v>
       </c>

--- a/Scenario Files/TestScenarios.xlsx
+++ b/Scenario Files/TestScenarios.xlsx
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +465,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>hvac_age</t>
+          <t>house_age</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -501,7 +502,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I'm working from home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm working from home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -531,8 +532,10 @@
       <c r="I2" t="n">
         <v>92</v>
       </c>
-      <c r="J2" t="n">
-        <v>20</v>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M2" t="n">
         <v>72</v>
@@ -554,7 +557,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I'm home all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -584,8 +587,10 @@
       <c r="I3" t="n">
         <v>20</v>
       </c>
-      <c r="J3" t="n">
-        <v>20</v>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M3" t="n">
         <v>68</v>
@@ -607,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 2 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -637,8 +642,10 @@
       <c r="I4" t="n">
         <v>90</v>
       </c>
-      <c r="J4" t="n">
-        <v>30</v>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>31-40 years</t>
+        </is>
       </c>
       <c r="M4" t="n">
         <v>77</v>
@@ -660,7 +667,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -690,8 +697,10 @@
       <c r="I5" t="n">
         <v>22</v>
       </c>
-      <c r="J5" t="n">
-        <v>30</v>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>31-40 years</t>
+        </is>
       </c>
       <c r="M5" t="n">
         <v>65</v>
@@ -713,7 +722,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what AC temperature should I set?</t>
+          <t>I'm gone most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -743,8 +752,10 @@
       <c r="I6" t="n">
         <v>86</v>
       </c>
-      <c r="J6" t="n">
-        <v>35</v>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>41-50 years</t>
+        </is>
       </c>
       <c r="M6" t="n">
         <v>74</v>
@@ -766,7 +777,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 1 person — what AC temperature should I set?</t>
+          <t>I'm planning to stay in all day with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -796,8 +807,10 @@
       <c r="I7" t="n">
         <v>93</v>
       </c>
-      <c r="J7" t="n">
-        <v>40</v>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>41-50 years</t>
+        </is>
       </c>
       <c r="M7" t="n">
         <v>78</v>
@@ -819,7 +832,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I'm around all day with 1 person — what heat temperature should I set?</t>
+          <t>I'm around all day with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -849,8 +862,10 @@
       <c r="I8" t="n">
         <v>24</v>
       </c>
-      <c r="J8" t="n">
-        <v>40</v>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>41-50 years</t>
+        </is>
       </c>
       <c r="M8" t="n">
         <v>64</v>
@@ -872,7 +887,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what AC temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,8 +917,10 @@
       <c r="I9" t="n">
         <v>89</v>
       </c>
-      <c r="J9" t="n">
-        <v>23</v>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M9" t="n">
         <v>76</v>
@@ -925,7 +942,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 2 people — what heat temperature should I set?</t>
+          <t>I'm spending the day at home with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -955,8 +972,10 @@
       <c r="I10" t="n">
         <v>26</v>
       </c>
-      <c r="J10" t="n">
-        <v>23</v>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M10" t="n">
         <v>67</v>
@@ -978,7 +997,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 2 people — what heat temperature should I set?</t>
+          <t>I'm not planning to leave today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1008,8 +1027,10 @@
       <c r="I11" t="n">
         <v>19</v>
       </c>
-      <c r="J11" t="n">
-        <v>12</v>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M11" t="n">
         <v>68</v>
@@ -1031,7 +1052,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1061,8 +1082,10 @@
       <c r="I12" t="n">
         <v>90</v>
       </c>
-      <c r="J12" t="n">
-        <v>5</v>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
       </c>
       <c r="M12" t="n">
         <v>76</v>
@@ -1084,7 +1107,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>I'm away most of today — what heat temperature should I set?</t>
+          <t>I'm away most of today, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1114,8 +1137,10 @@
       <c r="I13" t="n">
         <v>21</v>
       </c>
-      <c r="J13" t="n">
-        <v>5</v>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
       </c>
       <c r="M13" t="n">
         <v>66</v>
@@ -1137,7 +1162,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1167,8 +1192,10 @@
       <c r="I14" t="n">
         <v>94</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
       </c>
       <c r="M14" t="n">
         <v>76</v>
@@ -1190,7 +1217,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>I'm staying home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm staying home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1220,8 +1247,10 @@
       <c r="I15" t="n">
         <v>88</v>
       </c>
-      <c r="J15" t="n">
-        <v>2</v>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
       </c>
       <c r="M15" t="n">
         <v>73</v>
@@ -1243,7 +1272,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the rowhouse?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1273,8 +1302,10 @@
       <c r="I16" t="n">
         <v>92</v>
       </c>
-      <c r="J16" t="n">
-        <v>4</v>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
       </c>
       <c r="M16" t="n">
         <v>78</v>
@@ -1296,7 +1327,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the rowhouse?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1326,8 +1357,10 @@
       <c r="I17" t="n">
         <v>20</v>
       </c>
-      <c r="J17" t="n">
-        <v>4</v>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
       </c>
       <c r="M17" t="n">
         <v>65</v>
@@ -1349,7 +1382,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1379,8 +1412,10 @@
       <c r="I18" t="n">
         <v>84</v>
       </c>
-      <c r="J18" t="n">
-        <v>7</v>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>6-10 years</t>
+        </is>
       </c>
       <c r="M18" t="n">
         <v>75</v>
@@ -1402,7 +1437,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I'm not home today — what AC temperature should I set?</t>
+          <t>I'm not home today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1432,8 +1467,10 @@
       <c r="I19" t="n">
         <v>91</v>
       </c>
-      <c r="J19" t="n">
-        <v>9</v>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>6-10 years</t>
+        </is>
       </c>
       <c r="M19" t="n">
         <v>78</v>
@@ -1455,7 +1492,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 5 people — what AC temperature should I set?</t>
+          <t>I'm home and not going out with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1485,8 +1522,10 @@
       <c r="I20" t="n">
         <v>90</v>
       </c>
-      <c r="J20" t="n">
-        <v>11</v>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>6-10 years</t>
+        </is>
       </c>
       <c r="M20" t="n">
         <v>71</v>
@@ -1508,7 +1547,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I'm out for a couple hours — what heat temperature should I set for the townhouse?</t>
+          <t>I'm out for a couple hours, what heat temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1538,8 +1577,10 @@
       <c r="I21" t="n">
         <v>18</v>
       </c>
-      <c r="J21" t="n">
-        <v>12</v>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>11-15 years</t>
+        </is>
       </c>
       <c r="M21" t="n">
         <v>66</v>
@@ -1561,7 +1602,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I'm staying put today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying put today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1591,8 +1632,10 @@
       <c r="I22" t="n">
         <v>22</v>
       </c>
-      <c r="J22" t="n">
-        <v>16</v>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>11-15 years</t>
+        </is>
       </c>
       <c r="M22" t="n">
         <v>65</v>
@@ -1644,8 +1687,10 @@
       <c r="I23" t="n">
         <v>87</v>
       </c>
-      <c r="J23" t="n">
-        <v>19</v>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M23" t="n">
         <v>75</v>
@@ -1697,8 +1742,10 @@
       <c r="I24" t="n">
         <v>19</v>
       </c>
-      <c r="J24" t="n">
-        <v>19</v>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M24" t="n">
         <v>66</v>
@@ -1750,8 +1797,10 @@
       <c r="I25" t="n">
         <v>90</v>
       </c>
-      <c r="J25" t="n">
-        <v>25</v>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M25" t="n">
         <v>78</v>
@@ -1803,8 +1852,10 @@
       <c r="I26" t="n">
         <v>91</v>
       </c>
-      <c r="J26" t="n">
-        <v>26</v>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M26" t="n">
         <v>76</v>
@@ -1856,8 +1907,10 @@
       <c r="I27" t="n">
         <v>17</v>
       </c>
-      <c r="J27" t="n">
-        <v>30</v>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M27" t="n">
         <v>66</v>
@@ -1879,7 +1932,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1909,8 +1962,10 @@
       <c r="I28" t="n">
         <v>21</v>
       </c>
-      <c r="J28" t="n">
-        <v>95</v>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>101-110 years</t>
+        </is>
       </c>
       <c r="M28" t="n">
         <v>66</v>
@@ -1932,7 +1987,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I'm working from home today with 4 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1962,8 +2017,10 @@
       <c r="I29" t="n">
         <v>98</v>
       </c>
-      <c r="J29" t="n">
-        <v>35</v>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>31-40 years</t>
+        </is>
       </c>
       <c r="M29" t="n">
         <v>78</v>
@@ -1985,7 +2042,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I'm home all day with 5 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2015,8 +2072,10 @@
       <c r="I30" t="n">
         <v>97</v>
       </c>
-      <c r="J30" t="n">
-        <v>30</v>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>31-40 years</t>
+        </is>
       </c>
       <c r="M30" t="n">
         <v>79</v>
@@ -2038,7 +2097,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I'm running out for a short while — what AC temperature should I set for the townhouse?</t>
+          <t>I'm running out for a short while, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2068,8 +2127,10 @@
       <c r="I31" t="n">
         <v>91</v>
       </c>
-      <c r="J31" t="n">
-        <v>18</v>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M31" t="n">
         <v>77</v>
@@ -2091,7 +2152,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>I'm gone for a few hours — what AC temperature should I set for the townhouse?</t>
+          <t>I'm gone for a few hours, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2121,8 +2182,10 @@
       <c r="I32" t="n">
         <v>91</v>
       </c>
-      <c r="J32" t="n">
-        <v>8</v>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>6-10 years</t>
+        </is>
       </c>
       <c r="M32" t="n">
         <v>82</v>
@@ -2144,7 +2207,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2174,8 +2237,10 @@
       <c r="I33" t="n">
         <v>102</v>
       </c>
-      <c r="J33" t="n">
-        <v>25</v>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M33" t="n">
         <v>78</v>
@@ -2197,7 +2262,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I'm out of the house all day — what AC temperature should I set?</t>
+          <t>I'm out of the house all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2227,8 +2292,10 @@
       <c r="I34" t="n">
         <v>94</v>
       </c>
-      <c r="J34" t="n">
-        <v>28</v>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M34" t="n">
         <v>79</v>
@@ -2250,7 +2317,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2280,8 +2347,10 @@
       <c r="I35" t="n">
         <v>89</v>
       </c>
-      <c r="J35" t="n">
-        <v>28</v>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>31-40 years</t>
+        </is>
       </c>
       <c r="M35" t="n">
         <v>78</v>
@@ -2303,7 +2372,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>I'm away for the day — what heat temperature should I set?</t>
+          <t>I'm away for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2333,8 +2402,10 @@
       <c r="I36" t="n">
         <v>15</v>
       </c>
-      <c r="J36" t="n">
-        <v>25</v>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M36" t="n">
         <v>60</v>
@@ -2386,8 +2457,10 @@
       <c r="I37" t="n">
         <v>78</v>
       </c>
-      <c r="J37" t="n">
-        <v>12</v>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>11-15 years</t>
+        </is>
       </c>
       <c r="M37" t="n">
         <v>73</v>
@@ -2439,8 +2512,10 @@
       <c r="I38" t="n">
         <v>82</v>
       </c>
-      <c r="J38" t="n">
-        <v>8</v>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>6-10 years</t>
+        </is>
       </c>
       <c r="M38" t="n">
         <v>74</v>
@@ -2492,8 +2567,10 @@
       <c r="I39" t="n">
         <v>48</v>
       </c>
-      <c r="J39" t="n">
-        <v>16</v>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M39" t="n">
         <v>66</v>
@@ -2515,7 +2592,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm planning to stay in all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2545,8 +2622,10 @@
       <c r="I40" t="n">
         <v>42</v>
       </c>
-      <c r="J40" t="n">
-        <v>25</v>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M40" t="n">
         <v>65</v>
@@ -2598,8 +2677,10 @@
       <c r="I41" t="n">
         <v>40</v>
       </c>
-      <c r="J41" t="n">
-        <v>18</v>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M41" t="n">
         <v>66</v>
@@ -2621,7 +2702,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>I'm around all day with 3 people — what AC temperature should I set?</t>
+          <t>I'm around all day with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2651,8 +2732,10 @@
       <c r="I42" t="n">
         <v>95</v>
       </c>
-      <c r="J42" t="n">
-        <v>18</v>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M42" t="n">
         <v>71</v>
@@ -2674,7 +2757,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2704,8 +2787,10 @@
       <c r="I43" t="n">
         <v>22</v>
       </c>
-      <c r="J43" t="n">
-        <v>32</v>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>31-40 years</t>
+        </is>
       </c>
       <c r="M43" t="n">
         <v>65</v>
@@ -2727,7 +2812,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I'm going to be out all day — what AC temperature should I set?</t>
+          <t>I'm going to be out all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2757,8 +2842,10 @@
       <c r="I44" t="n">
         <v>92</v>
       </c>
-      <c r="J44" t="n">
-        <v>18</v>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M44" t="n">
         <v>78</v>
@@ -2780,7 +2867,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I'm leaving the house for most of the day — what AC temperature should I set?</t>
+          <t>I'm leaving the house for most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2810,8 +2897,10 @@
       <c r="I45" t="n">
         <v>88</v>
       </c>
-      <c r="J45" t="n">
-        <v>10</v>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>11-15 years</t>
+        </is>
       </c>
       <c r="M45" t="n">
         <v>78</v>
@@ -2833,7 +2922,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2863,8 +2952,10 @@
       <c r="I46" t="n">
         <v>84</v>
       </c>
-      <c r="J46" t="n">
-        <v>6</v>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>6-10 years</t>
+        </is>
       </c>
       <c r="M46" t="n">
         <v>73</v>
@@ -2886,7 +2977,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2916,8 +3007,10 @@
       <c r="I47" t="n">
         <v>12</v>
       </c>
-      <c r="J47" t="n">
-        <v>16</v>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M47" t="n">
         <v>65</v>
@@ -2939,7 +3032,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>We're about to turn in — what heat temperature should I set overnight?</t>
+          <t>We're about to turn in, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2969,8 +3062,10 @@
       <c r="I48" t="n">
         <v>20</v>
       </c>
-      <c r="J48" t="n">
-        <v>20</v>
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M48" t="n">
         <v>66</v>
@@ -3022,8 +3117,10 @@
       <c r="I49" t="n">
         <v>22</v>
       </c>
-      <c r="J49" t="n">
-        <v>1</v>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
       </c>
       <c r="M49" t="n">
         <v>67</v>
@@ -3045,7 +3142,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3075,8 +3172,10 @@
       <c r="I50" t="n">
         <v>28</v>
       </c>
-      <c r="J50" t="n">
-        <v>3</v>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
       </c>
       <c r="M50" t="n">
         <v>66</v>
@@ -3098,7 +3197,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 4 people — what AC temperature should I set?</t>
+          <t>I'm not planning to leave today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3128,8 +3227,10 @@
       <c r="I51" t="n">
         <v>94</v>
       </c>
-      <c r="J51" t="n">
-        <v>20</v>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M51" t="n">
         <v>70</v>
@@ -3181,8 +3282,10 @@
       <c r="I52" t="n">
         <v>91</v>
       </c>
-      <c r="J52" t="n">
-        <v>33</v>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>41-50 years</t>
+        </is>
       </c>
       <c r="M52" t="n">
         <v>74</v>
@@ -3234,8 +3337,10 @@
       <c r="I53" t="n">
         <v>68</v>
       </c>
-      <c r="J53" t="n">
-        <v>8</v>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>11-15 years</t>
+        </is>
       </c>
       <c r="M53" t="n">
         <v>68</v>
@@ -3257,7 +3362,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I'm staying home today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying home today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3287,8 +3392,10 @@
       <c r="I54" t="n">
         <v>8</v>
       </c>
-      <c r="J54" t="n">
-        <v>6</v>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M54" t="n">
         <v>66</v>
@@ -3310,7 +3417,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 4 people — what heat temperature should I set?</t>
+          <t>I'm home and not going out with 4 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3340,8 +3447,10 @@
       <c r="I55" t="n">
         <v>42</v>
       </c>
-      <c r="J55" t="n">
-        <v>11</v>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M55" t="n">
         <v>65</v>
@@ -3363,7 +3472,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3393,8 +3502,10 @@
       <c r="I56" t="n">
         <v>68</v>
       </c>
-      <c r="J56" t="n">
-        <v>3</v>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>11-15 years</t>
+        </is>
       </c>
       <c r="M56" t="n">
         <v>66</v>
@@ -3416,7 +3527,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3446,8 +3557,10 @@
       <c r="I57" t="n">
         <v>78</v>
       </c>
-      <c r="J57" t="n">
-        <v>7</v>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M57" t="n">
         <v>72</v>
@@ -3469,7 +3582,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>I'm home all day with 4 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3499,8 +3612,10 @@
       <c r="I58" t="n">
         <v>96</v>
       </c>
-      <c r="J58" t="n">
-        <v>4</v>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>6-10 years</t>
+        </is>
       </c>
       <c r="M58" t="n">
         <v>72</v>
@@ -3522,7 +3637,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 5 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3552,8 +3667,10 @@
       <c r="I59" t="n">
         <v>90</v>
       </c>
-      <c r="J59" t="n">
-        <v>21</v>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>81-90 years</t>
+        </is>
       </c>
       <c r="M59" t="n">
         <v>73</v>
@@ -3575,7 +3692,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3605,8 +3722,10 @@
       <c r="I60" t="n">
         <v>29</v>
       </c>
-      <c r="J60" t="n">
-        <v>15</v>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>41-50 years</t>
+        </is>
       </c>
       <c r="M60" t="n">
         <v>62</v>
@@ -3628,7 +3747,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 1 person — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3658,8 +3777,10 @@
       <c r="I61" t="n">
         <v>24</v>
       </c>
-      <c r="J61" t="n">
-        <v>6</v>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>11-15 years</t>
+        </is>
       </c>
       <c r="M61" t="n">
         <v>66</v>
@@ -3681,7 +3802,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>I'm staying in today with 3 people — what heat temperature should I set?</t>
+          <t>I'm staying in today with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3711,8 +3832,10 @@
       <c r="I62" t="n">
         <v>25</v>
       </c>
-      <c r="J62" t="n">
-        <v>18</v>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M62" t="n">
         <v>64</v>
@@ -3764,8 +3887,10 @@
       <c r="I63" t="n">
         <v>18</v>
       </c>
-      <c r="J63" t="n">
-        <v>24</v>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M63" t="n">
         <v>62</v>
@@ -3787,7 +3912,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3817,8 +3942,10 @@
       <c r="I64" t="n">
         <v>14</v>
       </c>
-      <c r="J64" t="n">
-        <v>28</v>
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t>31-40 years</t>
+        </is>
       </c>
       <c r="M64" t="n">
         <v>58</v>
@@ -3840,7 +3967,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>I'm around all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm around all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3870,8 +3997,10 @@
       <c r="I65" t="n">
         <v>28</v>
       </c>
-      <c r="J65" t="n">
-        <v>16</v>
+      <c r="J65" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M65" t="n">
         <v>64</v>
@@ -3893,7 +4022,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3923,8 +4052,10 @@
       <c r="I66" t="n">
         <v>10</v>
       </c>
-      <c r="J66" t="n">
-        <v>14</v>
+      <c r="J66" s="1" t="inlineStr">
+        <is>
+          <t>16-20 years</t>
+        </is>
       </c>
       <c r="M66" t="n">
         <v>60</v>
@@ -3946,7 +4077,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what heat temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3976,8 +4107,10 @@
       <c r="I67" t="n">
         <v>5</v>
       </c>
-      <c r="J67" t="n">
-        <v>32</v>
+      <c r="J67" s="1" t="inlineStr">
+        <is>
+          <t>31-40 years</t>
+        </is>
       </c>
       <c r="M67" t="n">
         <v>62</v>
@@ -3999,7 +4132,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4029,8 +4162,10 @@
       <c r="I68" t="n">
         <v>22</v>
       </c>
-      <c r="J68" t="n">
-        <v>22</v>
+      <c r="J68" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M68" t="n">
         <v>60</v>
@@ -4082,8 +4217,10 @@
       <c r="I69" t="n">
         <v>12</v>
       </c>
-      <c r="J69" t="n">
-        <v>20</v>
+      <c r="J69" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M69" t="n">
         <v>62</v>
@@ -4105,7 +4242,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4135,8 +4272,10 @@
       <c r="I70" t="n">
         <v>89</v>
       </c>
-      <c r="J70" t="n">
-        <v>12</v>
+      <c r="J70" s="1" t="inlineStr">
+        <is>
+          <t>11-15 years</t>
+        </is>
       </c>
       <c r="M70" t="n">
         <v>73</v>
@@ -4158,7 +4297,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4188,8 +4327,10 @@
       <c r="I71" t="n">
         <v>91</v>
       </c>
-      <c r="J71" t="n">
-        <v>18</v>
+      <c r="J71" s="1" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
       </c>
       <c r="M71" t="n">
         <v>78</v>
@@ -4395,7 +4536,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>It's just past 5 PM — when should I run the dryer?</t>
+          <t>It's just past 5 PM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4625,7 +4766,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>It's around 7 in the evening — when should I run the dishwasher?</t>
+          <t>It's around 7 in the evening, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4901,7 +5042,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>It's getting close to midnight — when should I run the washing machine?</t>
+          <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4947,7 +5088,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>It's just past 5 PM — when should I run the washer?</t>
+          <t>It's just past 5 PM, when should I run the washer?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5315,7 +5456,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>It's past 1 in the morning — when should I run the dryer?</t>
+          <t>It's past 1 in the morning, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5499,7 +5640,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>It's just past midnight — when should I run the dishwasher?</t>
+          <t>It's just past midnight, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5729,7 +5870,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>It's around 8 at night — when should I run the dishwasher?</t>
+          <t>It's around 8 at night, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7223,8 +7364,10 @@
       <c r="I137" t="n">
         <v>28</v>
       </c>
-      <c r="L137" t="n">
-        <v>1.5</v>
+      <c r="L137" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M137" t="n">
         <v>3</v>
@@ -7266,8 +7409,10 @@
       <c r="I138" t="n">
         <v>85</v>
       </c>
-      <c r="L138" t="n">
-        <v>1.5</v>
+      <c r="L138" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M138" t="n">
         <v>4</v>
@@ -7309,8 +7454,10 @@
       <c r="I139" t="n">
         <v>18</v>
       </c>
-      <c r="L139" t="n">
-        <v>1.5</v>
+      <c r="L139" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M139" t="n">
         <v>5</v>
@@ -7352,8 +7499,10 @@
       <c r="I140" t="n">
         <v>75</v>
       </c>
-      <c r="L140" t="n">
-        <v>2.5</v>
+      <c r="L140" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M140" t="n">
         <v>5</v>
@@ -7395,8 +7544,10 @@
       <c r="I141" t="n">
         <v>78</v>
       </c>
-      <c r="L141" t="n">
-        <v>1.5</v>
+      <c r="L141" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M141" t="n">
         <v>5</v>
@@ -7438,8 +7589,10 @@
       <c r="I142" t="n">
         <v>28</v>
       </c>
-      <c r="L142" t="n">
-        <v>2.5</v>
+      <c r="L142" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M142" t="n">
         <v>6</v>
@@ -7481,8 +7634,10 @@
       <c r="I143" t="n">
         <v>32</v>
       </c>
-      <c r="L143" t="n">
-        <v>1.5</v>
+      <c r="L143" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M143" t="n">
         <v>5</v>
@@ -7524,8 +7679,10 @@
       <c r="I144" t="n">
         <v>30</v>
       </c>
-      <c r="L144" t="n">
-        <v>1.5</v>
+      <c r="L144" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M144" t="n">
         <v>3</v>
@@ -7567,8 +7724,10 @@
       <c r="I145" t="n">
         <v>82</v>
       </c>
-      <c r="L145" t="n">
-        <v>2.5</v>
+      <c r="L145" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M145" t="n">
         <v>5</v>
@@ -7610,8 +7769,10 @@
       <c r="I146" t="n">
         <v>20</v>
       </c>
-      <c r="L146" t="n">
-        <v>3.5</v>
+      <c r="L146" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M146" t="n">
         <v>8</v>
@@ -7653,8 +7814,10 @@
       <c r="I147" t="n">
         <v>82</v>
       </c>
-      <c r="L147" t="n">
-        <v>3.5</v>
+      <c r="L147" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M147" t="n">
         <v>10</v>
@@ -7696,8 +7859,10 @@
       <c r="I148" t="n">
         <v>30</v>
       </c>
-      <c r="L148" t="n">
-        <v>2.5</v>
+      <c r="L148" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M148" t="n">
         <v>6</v>
@@ -7739,8 +7904,10 @@
       <c r="I149" t="n">
         <v>85</v>
       </c>
-      <c r="L149" t="n">
-        <v>2.5</v>
+      <c r="L149" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M149" t="n">
         <v>6</v>
@@ -7782,8 +7949,10 @@
       <c r="I150" t="n">
         <v>25</v>
       </c>
-      <c r="L150" t="n">
-        <v>3.5</v>
+      <c r="L150" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M150" t="n">
         <v>6</v>
@@ -7825,8 +7994,10 @@
       <c r="I151" t="n">
         <v>90</v>
       </c>
-      <c r="L151" t="n">
-        <v>3.5</v>
+      <c r="L151" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M151" t="n">
         <v>7</v>
@@ -7868,8 +8039,10 @@
       <c r="I152" t="n">
         <v>15</v>
       </c>
-      <c r="L152" t="n">
-        <v>4</v>
+      <c r="L152" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M152" t="n">
         <v>12</v>
@@ -7911,8 +8084,10 @@
       <c r="I153" t="n">
         <v>78</v>
       </c>
-      <c r="L153" t="n">
-        <v>2</v>
+      <c r="L153" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M153" t="n">
         <v>5</v>
@@ -7954,8 +8129,10 @@
       <c r="I154" t="n">
         <v>88</v>
       </c>
-      <c r="L154" t="n">
-        <v>4</v>
+      <c r="L154" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M154" t="n">
         <v>10</v>
@@ -7997,8 +8174,10 @@
       <c r="I155" t="n">
         <v>22</v>
       </c>
-      <c r="L155" t="n">
-        <v>2</v>
+      <c r="L155" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M155" t="n">
         <v>2</v>
@@ -8040,8 +8219,10 @@
       <c r="I156" t="n">
         <v>80</v>
       </c>
-      <c r="L156" t="n">
-        <v>2.5</v>
+      <c r="L156" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M156" t="n">
         <v>3</v>
@@ -8083,8 +8264,10 @@
       <c r="I157" t="n">
         <v>12</v>
       </c>
-      <c r="L157" t="n">
-        <v>3</v>
+      <c r="L157" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M157" t="n">
         <v>8</v>
@@ -8126,8 +8309,10 @@
       <c r="I158" t="n">
         <v>92</v>
       </c>
-      <c r="L158" t="n">
-        <v>2</v>
+      <c r="L158" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M158" t="n">
         <v>5</v>
@@ -8169,8 +8354,10 @@
       <c r="I159" t="n">
         <v>30</v>
       </c>
-      <c r="L159" t="n">
-        <v>3.5</v>
+      <c r="L159" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M159" t="n">
         <v>5</v>
@@ -8212,8 +8399,10 @@
       <c r="I160" t="n">
         <v>70</v>
       </c>
-      <c r="L160" t="n">
-        <v>3.5</v>
+      <c r="L160" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M160" t="n">
         <v>4</v>
@@ -8255,8 +8444,10 @@
       <c r="I161" t="n">
         <v>55</v>
       </c>
-      <c r="L161" t="n">
-        <v>4</v>
+      <c r="L161" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M161" t="n">
         <v>4</v>
@@ -8298,8 +8489,10 @@
       <c r="I162" t="n">
         <v>58</v>
       </c>
-      <c r="L162" t="n">
-        <v>2</v>
+      <c r="L162" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M162" t="n">
         <v>3</v>
@@ -8341,8 +8534,10 @@
       <c r="I163" t="n">
         <v>65</v>
       </c>
-      <c r="L163" t="n">
-        <v>2.5</v>
+      <c r="L163" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M163" t="n">
         <v>4</v>
@@ -8384,8 +8579,10 @@
       <c r="I164" t="n">
         <v>50</v>
       </c>
-      <c r="L164" t="n">
-        <v>2</v>
+      <c r="L164" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M164" t="n">
         <v>5</v>
@@ -8427,8 +8624,10 @@
       <c r="I165" t="n">
         <v>40</v>
       </c>
-      <c r="L165" t="n">
-        <v>2.5</v>
+      <c r="L165" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M165" t="n">
         <v>2</v>
@@ -8470,8 +8669,10 @@
       <c r="I166" t="n">
         <v>72</v>
       </c>
-      <c r="L166" t="n">
-        <v>2</v>
+      <c r="L166" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M166" t="n">
         <v>6</v>
@@ -8513,8 +8714,10 @@
       <c r="I167" t="n">
         <v>52</v>
       </c>
-      <c r="L167" t="n">
-        <v>2</v>
+      <c r="L167" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M167" t="n">
         <v>5</v>
@@ -8556,8 +8759,10 @@
       <c r="I168" t="n">
         <v>45</v>
       </c>
-      <c r="L168" t="n">
-        <v>2.5</v>
+      <c r="L168" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M168" t="n">
         <v>5</v>
@@ -8599,8 +8804,10 @@
       <c r="I169" t="n">
         <v>60</v>
       </c>
-      <c r="L169" t="n">
-        <v>2</v>
+      <c r="L169" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M169" t="n">
         <v>5</v>
@@ -8642,8 +8849,10 @@
       <c r="I170" t="n">
         <v>55</v>
       </c>
-      <c r="L170" t="n">
-        <v>2.5</v>
+      <c r="L170" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M170" t="n">
         <v>5</v>
@@ -8685,8 +8894,10 @@
       <c r="I171" t="n">
         <v>48</v>
       </c>
-      <c r="L171" t="n">
-        <v>2.5</v>
+      <c r="L171" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M171" t="n">
         <v>5</v>
@@ -8728,8 +8939,10 @@
       <c r="I172" t="n">
         <v>55</v>
       </c>
-      <c r="L172" t="n">
-        <v>2.5</v>
+      <c r="L172" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M172" t="n">
         <v>8</v>
@@ -8771,8 +8984,10 @@
       <c r="I173" t="n">
         <v>50</v>
       </c>
-      <c r="L173" t="n">
-        <v>3</v>
+      <c r="L173" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M173" t="n">
         <v>8</v>
@@ -8814,8 +9029,10 @@
       <c r="I174" t="n">
         <v>60</v>
       </c>
-      <c r="L174" t="n">
-        <v>2.5</v>
+      <c r="L174" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M174" t="n">
         <v>8</v>
@@ -8857,8 +9074,10 @@
       <c r="I175" t="n">
         <v>55</v>
       </c>
-      <c r="L175" t="n">
-        <v>2</v>
+      <c r="L175" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M175" t="n">
         <v>8</v>
@@ -8900,8 +9119,10 @@
       <c r="I176" t="n">
         <v>58</v>
       </c>
-      <c r="L176" t="n">
-        <v>2.5</v>
+      <c r="L176" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M176" t="n">
         <v>8</v>
@@ -8943,8 +9164,10 @@
       <c r="I177" t="n">
         <v>10</v>
       </c>
-      <c r="L177" t="n">
-        <v>2.5</v>
+      <c r="L177" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M177" t="n">
         <v>5</v>
@@ -8986,8 +9209,10 @@
       <c r="I178" t="n">
         <v>20</v>
       </c>
-      <c r="L178" t="n">
-        <v>2</v>
+      <c r="L178" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M178" t="n">
         <v>5</v>
@@ -9029,8 +9254,10 @@
       <c r="I179" t="n">
         <v>32</v>
       </c>
-      <c r="L179" t="n">
-        <v>2.5</v>
+      <c r="L179" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M179" t="n">
         <v>5</v>
@@ -9072,8 +9299,10 @@
       <c r="I180" t="n">
         <v>92</v>
       </c>
-      <c r="L180" t="n">
-        <v>2.5</v>
+      <c r="L180" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M180" t="n">
         <v>5</v>
@@ -9115,8 +9344,10 @@
       <c r="I181" t="n">
         <v>42</v>
       </c>
-      <c r="L181" t="n">
-        <v>3</v>
+      <c r="L181" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M181" t="n">
         <v>4</v>
@@ -9158,8 +9389,10 @@
       <c r="I182" t="n">
         <v>38</v>
       </c>
-      <c r="L182" t="n">
-        <v>4</v>
+      <c r="L182" s="1" t="inlineStr">
+        <is>
+          <t>high_flow</t>
+        </is>
       </c>
       <c r="M182" t="n">
         <v>4</v>
@@ -9201,8 +9434,10 @@
       <c r="I183" t="n">
         <v>55</v>
       </c>
-      <c r="L183" t="n">
-        <v>2</v>
+      <c r="L183" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M183" t="n">
         <v>1</v>
@@ -9244,8 +9479,10 @@
       <c r="I184" t="n">
         <v>62</v>
       </c>
-      <c r="L184" t="n">
-        <v>2.5</v>
+      <c r="L184" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M184" t="n">
         <v>7</v>
@@ -9287,8 +9524,10 @@
       <c r="I185" t="n">
         <v>50</v>
       </c>
-      <c r="L185" t="n">
-        <v>2</v>
+      <c r="L185" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M185" t="n">
         <v>5</v>
@@ -9330,8 +9569,10 @@
       <c r="I186" t="n">
         <v>58</v>
       </c>
-      <c r="L186" t="n">
-        <v>2.5</v>
+      <c r="L186" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M186" t="n">
         <v>5</v>
@@ -9373,8 +9614,10 @@
       <c r="I187" t="n">
         <v>55</v>
       </c>
-      <c r="L187" t="n">
-        <v>2.5</v>
+      <c r="L187" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M187" t="n">
         <v>6</v>
@@ -9416,8 +9659,10 @@
       <c r="I188" t="n">
         <v>58</v>
       </c>
-      <c r="L188" t="n">
-        <v>2.5</v>
+      <c r="L188" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M188" t="n">
         <v>8</v>
@@ -9459,8 +9704,10 @@
       <c r="I189" t="n">
         <v>5</v>
       </c>
-      <c r="L189" t="n">
-        <v>2</v>
+      <c r="L189" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M189" t="n">
         <v>5</v>
@@ -9502,8 +9749,10 @@
       <c r="I190" t="n">
         <v>65</v>
       </c>
-      <c r="L190" t="n">
-        <v>2</v>
+      <c r="L190" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M190" t="n">
         <v>3</v>
@@ -9545,8 +9794,10 @@
       <c r="I191" t="n">
         <v>78</v>
       </c>
-      <c r="L191" t="n">
-        <v>2.5</v>
+      <c r="L191" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M191" t="n">
         <v>3</v>
@@ -9588,8 +9839,10 @@
       <c r="I192" t="n">
         <v>72</v>
       </c>
-      <c r="L192" t="n">
-        <v>2.5</v>
+      <c r="L192" s="1" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
       </c>
       <c r="M192" t="n">
         <v>3</v>
@@ -9631,8 +9884,10 @@
       <c r="I193" t="n">
         <v>58</v>
       </c>
-      <c r="L193" t="n">
-        <v>2</v>
+      <c r="L193" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M193" t="n">
         <v>3</v>
@@ -9674,8 +9929,10 @@
       <c r="I194" t="n">
         <v>35</v>
       </c>
-      <c r="L194" t="n">
-        <v>1.5</v>
+      <c r="L194" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M194" t="n">
         <v>4</v>
@@ -9717,8 +9974,10 @@
       <c r="I195" t="n">
         <v>45</v>
       </c>
-      <c r="L195" t="n">
-        <v>2</v>
+      <c r="L195" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M195" t="n">
         <v>4</v>
@@ -9760,8 +10019,10 @@
       <c r="I196" t="n">
         <v>42</v>
       </c>
-      <c r="L196" t="n">
-        <v>2</v>
+      <c r="L196" s="1" t="inlineStr">
+        <is>
+          <t>low_flow</t>
+        </is>
       </c>
       <c r="M196" t="n">
         <v>3</v>
